--- a/docs/設計/製品在庫管理/基本設計書_製品在庫照会API .xlsx
+++ b/docs/設計/製品在庫管理/基本設計書_製品在庫照会API .xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="134">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -126,6 +126,9 @@
     <t>R</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>U</t>
   </si>
   <si>
@@ -135,7 +138,7 @@
     <t>共通機能</t>
   </si>
   <si>
-    <t>製品在庫テーブル</t>
+    <t>部品在庫テーブル</t>
   </si>
   <si>
     <t>◯</t>
@@ -480,8 +483,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="29">
@@ -541,68 +544,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -616,16 +558,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -647,15 +589,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -670,9 +627,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -684,8 +664,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -718,25 +721,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,7 +757,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,7 +835,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,31 +877,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,85 +895,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,26 +1056,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1116,30 +1117,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1148,6 +1125,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1156,7 +1159,7 @@
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1165,7 +1168,7 @@
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1174,134 +1177,134 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1431,9 +1434,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1487,9 +1496,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1617,6 +1623,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1658,6 +1673,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2350,7 +2368,7 @@
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.66666666666667" style="28"/>
-    <col min="2" max="2" width="5.11111111111111" style="110" customWidth="1"/>
+    <col min="2" max="2" width="5.11111111111111" style="114" customWidth="1"/>
     <col min="3" max="3" width="12.3333333333333" style="28" customWidth="1"/>
     <col min="4" max="4" width="10.3333333333333" style="28" customWidth="1"/>
     <col min="5" max="5" width="66.1111111111111" style="28" customWidth="1"/>
@@ -2363,428 +2381,428 @@
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="116" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="114">
+      <c r="C3" s="118">
         <v>45636</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="115" t="s">
+      <c r="E3" s="119" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="113"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="120"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="113"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="116"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="120"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="113"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="113"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="113"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
+      <c r="B8" s="117"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="113"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="115"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="113"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="113"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="113"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="113"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="113"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="113"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="113"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="113"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="113"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
+      <c r="B18" s="117"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="113"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="113"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="113"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="113"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="113"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="113"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="115"/>
-      <c r="E24" s="115"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="113"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="113"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="113"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="113"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
+      <c r="B28" s="117"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="113"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="113"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
+      <c r="B30" s="117"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="113"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="113"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
+      <c r="B32" s="117"/>
+      <c r="C32" s="119"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="113"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="119"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="113"/>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="119"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="119"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="113"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
+      <c r="B35" s="117"/>
+      <c r="C35" s="119"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="113"/>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="113"/>
-      <c r="C37" s="115"/>
-      <c r="D37" s="115"/>
-      <c r="E37" s="115"/>
+      <c r="B37" s="117"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="113"/>
-      <c r="C38" s="115"/>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
+      <c r="B38" s="117"/>
+      <c r="C38" s="119"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="119"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="113"/>
-      <c r="C39" s="115"/>
-      <c r="D39" s="115"/>
-      <c r="E39" s="115"/>
+      <c r="B39" s="117"/>
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="113"/>
-      <c r="C40" s="115"/>
-      <c r="D40" s="115"/>
-      <c r="E40" s="115"/>
+      <c r="B40" s="117"/>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="113"/>
-      <c r="C41" s="115"/>
-      <c r="D41" s="115"/>
-      <c r="E41" s="115"/>
+      <c r="B41" s="117"/>
+      <c r="C41" s="119"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="119"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="113"/>
-      <c r="C42" s="115"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="115"/>
+      <c r="B42" s="117"/>
+      <c r="C42" s="119"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="119"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="113"/>
-      <c r="C43" s="115"/>
-      <c r="D43" s="115"/>
-      <c r="E43" s="115"/>
+      <c r="B43" s="117"/>
+      <c r="C43" s="119"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="119"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="113"/>
-      <c r="C44" s="115"/>
-      <c r="D44" s="115"/>
-      <c r="E44" s="115"/>
+      <c r="B44" s="117"/>
+      <c r="C44" s="119"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="113"/>
-      <c r="C45" s="115"/>
-      <c r="D45" s="115"/>
-      <c r="E45" s="115"/>
+      <c r="B45" s="117"/>
+      <c r="C45" s="119"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="113"/>
-      <c r="C46" s="115"/>
-      <c r="D46" s="115"/>
-      <c r="E46" s="115"/>
+      <c r="B46" s="117"/>
+      <c r="C46" s="119"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="119"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="113"/>
-      <c r="C47" s="115"/>
-      <c r="D47" s="115"/>
-      <c r="E47" s="115"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="119"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="119"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="113"/>
-      <c r="C48" s="115"/>
-      <c r="D48" s="115"/>
-      <c r="E48" s="115"/>
+      <c r="B48" s="117"/>
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="113"/>
-      <c r="C49" s="115"/>
-      <c r="D49" s="115"/>
-      <c r="E49" s="115"/>
+      <c r="B49" s="117"/>
+      <c r="C49" s="119"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="119"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="113"/>
-      <c r="C50" s="115"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="115"/>
+      <c r="B50" s="117"/>
+      <c r="C50" s="119"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="119"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="113"/>
-      <c r="C51" s="115"/>
-      <c r="D51" s="115"/>
-      <c r="E51" s="115"/>
+      <c r="B51" s="117"/>
+      <c r="C51" s="119"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="119"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="113"/>
-      <c r="C52" s="115"/>
-      <c r="D52" s="115"/>
-      <c r="E52" s="115"/>
+      <c r="B52" s="117"/>
+      <c r="C52" s="119"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="119"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="113"/>
-      <c r="C53" s="115"/>
-      <c r="D53" s="115"/>
-      <c r="E53" s="115"/>
+      <c r="B53" s="117"/>
+      <c r="C53" s="119"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="119"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="113"/>
-      <c r="C54" s="115"/>
-      <c r="D54" s="115"/>
-      <c r="E54" s="115"/>
+      <c r="B54" s="117"/>
+      <c r="C54" s="119"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="119"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="113"/>
-      <c r="C55" s="115"/>
-      <c r="D55" s="115"/>
-      <c r="E55" s="115"/>
+      <c r="B55" s="117"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="119"/>
+      <c r="E55" s="119"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="113"/>
-      <c r="C56" s="115"/>
-      <c r="D56" s="115"/>
-      <c r="E56" s="115"/>
+      <c r="B56" s="117"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="119"/>
+      <c r="E56" s="119"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="113"/>
-      <c r="C57" s="115"/>
-      <c r="D57" s="115"/>
-      <c r="E57" s="115"/>
+      <c r="B57" s="117"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="119"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="113"/>
-      <c r="C58" s="115"/>
-      <c r="D58" s="115"/>
-      <c r="E58" s="115"/>
+      <c r="B58" s="117"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="119"/>
+      <c r="E58" s="119"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="113"/>
-      <c r="C59" s="115"/>
-      <c r="D59" s="115"/>
-      <c r="E59" s="115"/>
+      <c r="B59" s="117"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="119"/>
+      <c r="E59" s="119"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="113"/>
-      <c r="C60" s="115"/>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
+      <c r="B60" s="117"/>
+      <c r="C60" s="119"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="113"/>
-      <c r="C61" s="115"/>
-      <c r="D61" s="115"/>
-      <c r="E61" s="115"/>
+      <c r="B61" s="117"/>
+      <c r="C61" s="119"/>
+      <c r="D61" s="119"/>
+      <c r="E61" s="119"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="113"/>
-      <c r="C62" s="115"/>
-      <c r="D62" s="115"/>
-      <c r="E62" s="115"/>
+      <c r="B62" s="117"/>
+      <c r="C62" s="119"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="119"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="113"/>
-      <c r="C63" s="115"/>
-      <c r="D63" s="115"/>
-      <c r="E63" s="115"/>
+      <c r="B63" s="117"/>
+      <c r="C63" s="119"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="119"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="113"/>
-      <c r="C64" s="115"/>
-      <c r="D64" s="115"/>
-      <c r="E64" s="115"/>
+      <c r="B64" s="117"/>
+      <c r="C64" s="119"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="119"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="113"/>
-      <c r="C65" s="115"/>
-      <c r="D65" s="115"/>
-      <c r="E65" s="115"/>
+      <c r="B65" s="117"/>
+      <c r="C65" s="119"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="113"/>
-      <c r="C66" s="115"/>
-      <c r="D66" s="115"/>
-      <c r="E66" s="115"/>
+      <c r="B66" s="117"/>
+      <c r="C66" s="119"/>
+      <c r="D66" s="119"/>
+      <c r="E66" s="119"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="113"/>
-      <c r="C67" s="115"/>
-      <c r="D67" s="115"/>
-      <c r="E67" s="115"/>
+      <c r="B67" s="117"/>
+      <c r="C67" s="119"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="119"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="113"/>
-      <c r="C68" s="115"/>
-      <c r="D68" s="115"/>
-      <c r="E68" s="115"/>
+      <c r="B68" s="117"/>
+      <c r="C68" s="119"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="119"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="113"/>
-      <c r="C69" s="115"/>
-      <c r="D69" s="115"/>
-      <c r="E69" s="115"/>
+      <c r="B69" s="117"/>
+      <c r="C69" s="119"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2798,11 +2816,11 @@
   <dimension ref="A1:AH25"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="3.66666666666667" style="78"/>
-    <col min="21" max="21" width="5.86666666666667" style="78" customWidth="1"/>
-    <col min="22" max="33" width="3.66666666666667" style="78"/>
-    <col min="34" max="34" width="13.0148148148148" style="78" customWidth="1"/>
-    <col min="35" max="16384" width="3.66666666666667" style="78"/>
+    <col min="1" max="20" width="3.66666666666667" style="79"/>
+    <col min="21" max="21" width="5.86666666666667" style="79" customWidth="1"/>
+    <col min="22" max="33" width="3.66666666666667" style="79"/>
+    <col min="34" max="34" width="13.0148148148148" style="79" customWidth="1"/>
+    <col min="35" max="16384" width="3.66666666666667" style="79"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:34">
@@ -2818,14 +2836,14 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="99"/>
+      <c r="K1" s="100"/>
       <c r="L1" s="34" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="35"/>
       <c r="N1" s="35"/>
       <c r="O1" s="35"/>
-      <c r="P1" s="65"/>
+      <c r="P1" s="66"/>
       <c r="Q1" s="36" t="s">
         <v>10</v>
       </c>
@@ -2833,27 +2851,27 @@
       <c r="S1" s="37"/>
       <c r="T1" s="37"/>
       <c r="U1" s="37"/>
-      <c r="V1" s="44" t="s">
+      <c r="V1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="45" t="s">
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="106"/>
-      <c r="AC1" s="47" t="s">
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="110"/>
+      <c r="AC1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="107"/>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="117" t="s">
+      <c r="AD1" s="111"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="74"/>
-      <c r="AH1" s="74"/>
+      <c r="AG1" s="75"/>
+      <c r="AH1" s="75"/>
     </row>
     <row r="2" customHeight="1" spans="1:34">
       <c r="A2" s="7"/>
@@ -2866,30 +2884,30 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="100"/>
+      <c r="K2" s="101"/>
       <c r="L2" s="38"/>
       <c r="M2" s="39"/>
       <c r="N2" s="39"/>
       <c r="O2" s="39"/>
-      <c r="P2" s="66"/>
+      <c r="P2" s="67"/>
       <c r="Q2" s="40"/>
       <c r="R2" s="41"/>
       <c r="S2" s="41"/>
       <c r="T2" s="41"/>
       <c r="U2" s="41"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="109"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="75"/>
-      <c r="AH2" s="75"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="76"/>
+      <c r="AH2" s="76"/>
     </row>
     <row r="3" customHeight="1" spans="1:34">
       <c r="A3" s="7"/>
@@ -2902,14 +2920,14 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="100"/>
+      <c r="K3" s="101"/>
       <c r="L3" s="34" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="35"/>
       <c r="N3" s="35"/>
       <c r="O3" s="35"/>
-      <c r="P3" s="65"/>
+      <c r="P3" s="66"/>
       <c r="Q3" s="36" t="s">
         <v>14</v>
       </c>
@@ -2917,27 +2935,27 @@
       <c r="S3" s="37"/>
       <c r="T3" s="37"/>
       <c r="U3" s="37"/>
-      <c r="V3" s="44" t="s">
+      <c r="V3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="45" t="s">
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="106"/>
-      <c r="AC3" s="44" t="s">
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="110"/>
+      <c r="AC3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="117" t="s">
+      <c r="AD3" s="46"/>
+      <c r="AE3" s="46"/>
+      <c r="AF3" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="74"/>
-      <c r="AH3" s="74"/>
+      <c r="AG3" s="75"/>
+      <c r="AH3" s="75"/>
     </row>
     <row r="4" customHeight="1" spans="1:34">
       <c r="A4" s="9"/>
@@ -2950,833 +2968,835 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
-      <c r="K4" s="101"/>
+      <c r="K4" s="102"/>
       <c r="L4" s="38"/>
       <c r="M4" s="39"/>
       <c r="N4" s="39"/>
       <c r="O4" s="39"/>
-      <c r="P4" s="66"/>
+      <c r="P4" s="67"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="41"/>
       <c r="S4" s="41"/>
       <c r="T4" s="41"/>
       <c r="U4" s="41"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="109"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="75"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="76"/>
+      <c r="AH4" s="76"/>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="82" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="102"/>
-      <c r="AF5" s="102"/>
-      <c r="AG5" s="102"/>
-      <c r="AH5" s="102"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
+      <c r="Y5" s="103"/>
+      <c r="Z5" s="103"/>
+      <c r="AA5" s="103"/>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="103"/>
+      <c r="AD5" s="103"/>
+      <c r="AE5" s="103"/>
+      <c r="AF5" s="103"/>
+      <c r="AG5" s="103"/>
+      <c r="AH5" s="103"/>
     </row>
     <row r="6" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="82" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="102"/>
-      <c r="S6" s="102"/>
-      <c r="T6" s="102"/>
-      <c r="U6" s="102"/>
-      <c r="V6" s="102"/>
-      <c r="W6" s="102"/>
-      <c r="X6" s="102"/>
-      <c r="Y6" s="102"/>
-      <c r="Z6" s="102"/>
-      <c r="AA6" s="102"/>
-      <c r="AB6" s="102"/>
-      <c r="AC6" s="102"/>
-      <c r="AD6" s="102"/>
-      <c r="AE6" s="102"/>
-      <c r="AF6" s="102"/>
-      <c r="AG6" s="102"/>
-      <c r="AH6" s="102"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="103"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="103"/>
+      <c r="V6" s="103"/>
+      <c r="W6" s="103"/>
+      <c r="X6" s="103"/>
+      <c r="Y6" s="103"/>
+      <c r="Z6" s="103"/>
+      <c r="AA6" s="103"/>
+      <c r="AB6" s="103"/>
+      <c r="AC6" s="103"/>
+      <c r="AD6" s="103"/>
+      <c r="AE6" s="103"/>
+      <c r="AF6" s="103"/>
+      <c r="AG6" s="103"/>
+      <c r="AH6" s="103"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="82" t="s">
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="102"/>
-      <c r="X7" s="102"/>
-      <c r="Y7" s="102"/>
-      <c r="Z7" s="102"/>
-      <c r="AA7" s="102"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="102"/>
-      <c r="AD7" s="102"/>
-      <c r="AE7" s="102"/>
-      <c r="AF7" s="102"/>
-      <c r="AG7" s="102"/>
-      <c r="AH7" s="102"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="103"/>
+      <c r="Y7" s="103"/>
+      <c r="Z7" s="103"/>
+      <c r="AA7" s="103"/>
+      <c r="AB7" s="103"/>
+      <c r="AC7" s="103"/>
+      <c r="AD7" s="103"/>
+      <c r="AE7" s="103"/>
+      <c r="AF7" s="103"/>
+      <c r="AG7" s="103"/>
+      <c r="AH7" s="103"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="82" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="102"/>
-      <c r="AE8" s="102"/>
-      <c r="AF8" s="102"/>
-      <c r="AG8" s="102"/>
-      <c r="AH8" s="102"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
+      <c r="K8" s="103"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="103"/>
+      <c r="O8" s="103"/>
+      <c r="P8" s="103"/>
+      <c r="Q8" s="103"/>
+      <c r="R8" s="103"/>
+      <c r="S8" s="103"/>
+      <c r="T8" s="103"/>
+      <c r="U8" s="103"/>
+      <c r="V8" s="103"/>
+      <c r="W8" s="103"/>
+      <c r="X8" s="103"/>
+      <c r="Y8" s="103"/>
+      <c r="Z8" s="103"/>
+      <c r="AA8" s="103"/>
+      <c r="AB8" s="103"/>
+      <c r="AC8" s="103"/>
+      <c r="AD8" s="103"/>
+      <c r="AE8" s="103"/>
+      <c r="AF8" s="103"/>
+      <c r="AG8" s="103"/>
+      <c r="AH8" s="103"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="82" t="s">
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="102"/>
-      <c r="S9" s="102"/>
-      <c r="T9" s="102"/>
-      <c r="U9" s="102"/>
-      <c r="V9" s="102"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="102"/>
-      <c r="Y9" s="102"/>
-      <c r="Z9" s="102"/>
-      <c r="AA9" s="102"/>
-      <c r="AB9" s="102"/>
-      <c r="AC9" s="102"/>
-      <c r="AD9" s="102"/>
-      <c r="AE9" s="102"/>
-      <c r="AF9" s="102"/>
-      <c r="AG9" s="102"/>
-      <c r="AH9" s="102"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="103"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="103"/>
+      <c r="P9" s="103"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="103"/>
+      <c r="S9" s="103"/>
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="103"/>
+      <c r="Z9" s="103"/>
+      <c r="AA9" s="103"/>
+      <c r="AB9" s="103"/>
+      <c r="AC9" s="103"/>
+      <c r="AD9" s="103"/>
+      <c r="AE9" s="103"/>
+      <c r="AF9" s="103"/>
+      <c r="AG9" s="103"/>
+      <c r="AH9" s="103"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="86" t="s">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="103"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="103"/>
-      <c r="L10" s="103"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="103"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="103"/>
-      <c r="S10" s="103"/>
-      <c r="T10" s="103"/>
-      <c r="U10" s="103"/>
-      <c r="V10" s="103"/>
-      <c r="W10" s="103"/>
-      <c r="X10" s="103"/>
-      <c r="Y10" s="103"/>
-      <c r="Z10" s="103"/>
-      <c r="AA10" s="103"/>
-      <c r="AB10" s="103"/>
-      <c r="AC10" s="103"/>
-      <c r="AD10" s="103"/>
-      <c r="AE10" s="103"/>
-      <c r="AF10" s="103"/>
-      <c r="AG10" s="103"/>
-      <c r="AH10" s="103"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="104"/>
+      <c r="Q10" s="104"/>
+      <c r="R10" s="104"/>
+      <c r="S10" s="104"/>
+      <c r="T10" s="104"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="104"/>
+      <c r="W10" s="104"/>
+      <c r="X10" s="104"/>
+      <c r="Y10" s="104"/>
+      <c r="Z10" s="104"/>
+      <c r="AA10" s="104"/>
+      <c r="AB10" s="104"/>
+      <c r="AC10" s="104"/>
+      <c r="AD10" s="104"/>
+      <c r="AE10" s="104"/>
+      <c r="AF10" s="104"/>
+      <c r="AG10" s="104"/>
+      <c r="AH10" s="104"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="88"/>
-      <c r="AF11" s="88"/>
-      <c r="AG11" s="88"/>
-      <c r="AH11" s="88"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="89"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="89"/>
+      <c r="N11" s="89"/>
+      <c r="O11" s="89"/>
+      <c r="P11" s="89"/>
+      <c r="Q11" s="89"/>
+      <c r="R11" s="89"/>
+      <c r="S11" s="89"/>
+      <c r="T11" s="89"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="89"/>
+      <c r="W11" s="89"/>
+      <c r="X11" s="89"/>
+      <c r="Y11" s="89"/>
+      <c r="Z11" s="89"/>
+      <c r="AA11" s="89"/>
+      <c r="AB11" s="89"/>
+      <c r="AC11" s="89"/>
+      <c r="AD11" s="89"/>
+      <c r="AE11" s="89"/>
+      <c r="AF11" s="89"/>
+      <c r="AG11" s="89"/>
+      <c r="AH11" s="89"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A12" s="89"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="90"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="S12" s="90"/>
-      <c r="T12" s="90"/>
-      <c r="U12" s="90"/>
-      <c r="V12" s="90"/>
-      <c r="W12" s="90"/>
-      <c r="X12" s="90"/>
-      <c r="Y12" s="90"/>
-      <c r="Z12" s="90"/>
-      <c r="AA12" s="90"/>
-      <c r="AB12" s="90"/>
-      <c r="AC12" s="90"/>
-      <c r="AD12" s="90"/>
-      <c r="AE12" s="90"/>
-      <c r="AF12" s="90"/>
-      <c r="AG12" s="90"/>
-      <c r="AH12" s="90"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="91"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="91"/>
+      <c r="U12" s="91"/>
+      <c r="V12" s="91"/>
+      <c r="W12" s="91"/>
+      <c r="X12" s="91"/>
+      <c r="Y12" s="91"/>
+      <c r="Z12" s="91"/>
+      <c r="AA12" s="91"/>
+      <c r="AB12" s="91"/>
+      <c r="AC12" s="91"/>
+      <c r="AD12" s="91"/>
+      <c r="AE12" s="91"/>
+      <c r="AF12" s="91"/>
+      <c r="AG12" s="91"/>
+      <c r="AH12" s="91"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A13" s="89"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
-      <c r="V13" s="90"/>
-      <c r="W13" s="90"/>
-      <c r="X13" s="90"/>
-      <c r="Y13" s="90"/>
-      <c r="Z13" s="90"/>
-      <c r="AA13" s="90"/>
-      <c r="AB13" s="90"/>
-      <c r="AC13" s="90"/>
-      <c r="AD13" s="90"/>
-      <c r="AE13" s="90"/>
-      <c r="AF13" s="90"/>
-      <c r="AG13" s="90"/>
-      <c r="AH13" s="90"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
+      <c r="R13" s="91"/>
+      <c r="S13" s="91"/>
+      <c r="T13" s="91"/>
+      <c r="U13" s="91"/>
+      <c r="V13" s="91"/>
+      <c r="W13" s="91"/>
+      <c r="X13" s="91"/>
+      <c r="Y13" s="91"/>
+      <c r="Z13" s="91"/>
+      <c r="AA13" s="91"/>
+      <c r="AB13" s="91"/>
+      <c r="AC13" s="91"/>
+      <c r="AD13" s="91"/>
+      <c r="AE13" s="91"/>
+      <c r="AF13" s="91"/>
+      <c r="AG13" s="91"/>
+      <c r="AH13" s="91"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A14" s="89"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
-      <c r="V14" s="90"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="90"/>
-      <c r="Y14" s="90"/>
-      <c r="Z14" s="90"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="90"/>
-      <c r="AC14" s="90"/>
-      <c r="AD14" s="90"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="90"/>
-      <c r="AG14" s="90"/>
-      <c r="AH14" s="90"/>
+      <c r="A14" s="90"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="91"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="91"/>
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="91"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="91"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
-      <c r="V15" s="90"/>
-      <c r="W15" s="90"/>
-      <c r="X15" s="90"/>
-      <c r="Y15" s="90"/>
-      <c r="Z15" s="90"/>
-      <c r="AA15" s="90"/>
-      <c r="AB15" s="90"/>
-      <c r="AC15" s="90"/>
-      <c r="AD15" s="90"/>
-      <c r="AE15" s="90"/>
-      <c r="AF15" s="90"/>
-      <c r="AG15" s="90"/>
-      <c r="AH15" s="90"/>
+      <c r="A15" s="90"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="91"/>
+      <c r="S15" s="91"/>
+      <c r="T15" s="91"/>
+      <c r="U15" s="91"/>
+      <c r="V15" s="91"/>
+      <c r="W15" s="91"/>
+      <c r="X15" s="91"/>
+      <c r="Y15" s="91"/>
+      <c r="Z15" s="91"/>
+      <c r="AA15" s="91"/>
+      <c r="AB15" s="91"/>
+      <c r="AC15" s="91"/>
+      <c r="AD15" s="91"/>
+      <c r="AE15" s="91"/>
+      <c r="AF15" s="91"/>
+      <c r="AG15" s="91"/>
+      <c r="AH15" s="91"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A16" s="89"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="90"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="90"/>
-      <c r="M16" s="90"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="90"/>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="90"/>
-      <c r="S16" s="90"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="90"/>
-      <c r="V16" s="90"/>
-      <c r="W16" s="90"/>
-      <c r="X16" s="90"/>
-      <c r="Y16" s="90"/>
-      <c r="Z16" s="90"/>
-      <c r="AA16" s="90"/>
-      <c r="AB16" s="90"/>
-      <c r="AC16" s="90"/>
-      <c r="AD16" s="90"/>
-      <c r="AE16" s="90"/>
-      <c r="AF16" s="90"/>
-      <c r="AG16" s="90"/>
-      <c r="AH16" s="90"/>
+      <c r="A16" s="90"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="91"/>
+      <c r="K16" s="91"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="91"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="91"/>
+      <c r="Q16" s="91"/>
+      <c r="R16" s="91"/>
+      <c r="S16" s="91"/>
+      <c r="T16" s="91"/>
+      <c r="U16" s="91"/>
+      <c r="V16" s="91"/>
+      <c r="W16" s="91"/>
+      <c r="X16" s="91"/>
+      <c r="Y16" s="91"/>
+      <c r="Z16" s="91"/>
+      <c r="AA16" s="91"/>
+      <c r="AB16" s="91"/>
+      <c r="AC16" s="91"/>
+      <c r="AD16" s="91"/>
+      <c r="AE16" s="91"/>
+      <c r="AF16" s="91"/>
+      <c r="AG16" s="91"/>
+      <c r="AH16" s="91"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A17" s="89"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="90"/>
-      <c r="X17" s="90"/>
-      <c r="Y17" s="90"/>
-      <c r="Z17" s="90"/>
-      <c r="AA17" s="90"/>
-      <c r="AB17" s="90"/>
-      <c r="AC17" s="90"/>
-      <c r="AD17" s="90"/>
-      <c r="AE17" s="90"/>
-      <c r="AF17" s="90"/>
-      <c r="AG17" s="90"/>
-      <c r="AH17" s="90"/>
+      <c r="A17" s="90"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="91"/>
+      <c r="S17" s="91"/>
+      <c r="T17" s="91"/>
+      <c r="U17" s="91"/>
+      <c r="V17" s="91"/>
+      <c r="W17" s="91"/>
+      <c r="X17" s="91"/>
+      <c r="Y17" s="91"/>
+      <c r="Z17" s="91"/>
+      <c r="AA17" s="91"/>
+      <c r="AB17" s="91"/>
+      <c r="AC17" s="91"/>
+      <c r="AD17" s="91"/>
+      <c r="AE17" s="91"/>
+      <c r="AF17" s="91"/>
+      <c r="AG17" s="91"/>
+      <c r="AH17" s="91"/>
     </row>
     <row r="18" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A18" s="89"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="90"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="90"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="90"/>
-      <c r="W18" s="90"/>
-      <c r="X18" s="90"/>
-      <c r="Y18" s="90"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="90"/>
-      <c r="AB18" s="90"/>
-      <c r="AC18" s="90"/>
-      <c r="AD18" s="90"/>
-      <c r="AE18" s="90"/>
-      <c r="AF18" s="90"/>
-      <c r="AG18" s="90"/>
-      <c r="AH18" s="90"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="91"/>
+      <c r="S18" s="91"/>
+      <c r="T18" s="91"/>
+      <c r="U18" s="91"/>
+      <c r="V18" s="91"/>
+      <c r="W18" s="91"/>
+      <c r="X18" s="91"/>
+      <c r="Y18" s="91"/>
+      <c r="Z18" s="91"/>
+      <c r="AA18" s="91"/>
+      <c r="AB18" s="91"/>
+      <c r="AC18" s="91"/>
+      <c r="AD18" s="91"/>
+      <c r="AE18" s="91"/>
+      <c r="AF18" s="91"/>
+      <c r="AG18" s="91"/>
+      <c r="AH18" s="91"/>
     </row>
     <row r="19" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A19" s="89"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="X19" s="90"/>
-      <c r="Y19" s="90"/>
-      <c r="Z19" s="90"/>
-      <c r="AA19" s="90"/>
-      <c r="AB19" s="90"/>
-      <c r="AC19" s="90"/>
-      <c r="AD19" s="90"/>
-      <c r="AE19" s="90"/>
-      <c r="AF19" s="90"/>
-      <c r="AG19" s="90"/>
-      <c r="AH19" s="90"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="91"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="91"/>
+      <c r="Q19" s="91"/>
+      <c r="R19" s="91"/>
+      <c r="S19" s="91"/>
+      <c r="T19" s="91"/>
+      <c r="U19" s="91"/>
+      <c r="V19" s="91"/>
+      <c r="W19" s="91"/>
+      <c r="X19" s="91"/>
+      <c r="Y19" s="91"/>
+      <c r="Z19" s="91"/>
+      <c r="AA19" s="91"/>
+      <c r="AB19" s="91"/>
+      <c r="AC19" s="91"/>
+      <c r="AD19" s="91"/>
+      <c r="AE19" s="91"/>
+      <c r="AF19" s="91"/>
+      <c r="AG19" s="91"/>
+      <c r="AH19" s="91"/>
     </row>
     <row r="20" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A20" s="89"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="U20" s="90"/>
-      <c r="V20" s="90"/>
-      <c r="W20" s="90"/>
-      <c r="X20" s="90"/>
-      <c r="Y20" s="90"/>
-      <c r="Z20" s="90"/>
-      <c r="AA20" s="90"/>
-      <c r="AB20" s="90"/>
-      <c r="AC20" s="90"/>
-      <c r="AD20" s="90"/>
-      <c r="AE20" s="90"/>
-      <c r="AF20" s="90"/>
-      <c r="AG20" s="90"/>
-      <c r="AH20" s="90"/>
+      <c r="A20" s="90"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
+      <c r="Q20" s="91"/>
+      <c r="R20" s="91"/>
+      <c r="S20" s="91"/>
+      <c r="T20" s="91"/>
+      <c r="U20" s="91"/>
+      <c r="V20" s="91"/>
+      <c r="W20" s="91"/>
+      <c r="X20" s="91"/>
+      <c r="Y20" s="91"/>
+      <c r="Z20" s="91"/>
+      <c r="AA20" s="91"/>
+      <c r="AB20" s="91"/>
+      <c r="AC20" s="91"/>
+      <c r="AD20" s="91"/>
+      <c r="AE20" s="91"/>
+      <c r="AF20" s="91"/>
+      <c r="AG20" s="91"/>
+      <c r="AH20" s="91"/>
     </row>
     <row r="21" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A21" s="89"/>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="90"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="T21" s="90"/>
-      <c r="U21" s="90"/>
-      <c r="V21" s="90"/>
-      <c r="W21" s="90"/>
-      <c r="X21" s="90"/>
-      <c r="Y21" s="90"/>
-      <c r="Z21" s="90"/>
-      <c r="AA21" s="90"/>
-      <c r="AB21" s="90"/>
-      <c r="AC21" s="90"/>
-      <c r="AD21" s="90"/>
-      <c r="AE21" s="90"/>
-      <c r="AF21" s="90"/>
-      <c r="AG21" s="90"/>
-      <c r="AH21" s="90"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="91"/>
+      <c r="P21" s="91"/>
+      <c r="Q21" s="91"/>
+      <c r="R21" s="91"/>
+      <c r="S21" s="91"/>
+      <c r="T21" s="91"/>
+      <c r="U21" s="91"/>
+      <c r="V21" s="91"/>
+      <c r="W21" s="91"/>
+      <c r="X21" s="91"/>
+      <c r="Y21" s="91"/>
+      <c r="Z21" s="91"/>
+      <c r="AA21" s="91"/>
+      <c r="AB21" s="91"/>
+      <c r="AC21" s="91"/>
+      <c r="AD21" s="91"/>
+      <c r="AE21" s="91"/>
+      <c r="AF21" s="91"/>
+      <c r="AG21" s="91"/>
+      <c r="AH21" s="91"/>
     </row>
     <row r="22" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A22" s="89"/>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="90"/>
-      <c r="U22" s="90"/>
-      <c r="V22" s="90"/>
-      <c r="W22" s="90"/>
-      <c r="X22" s="90"/>
-      <c r="Y22" s="90"/>
-      <c r="Z22" s="90"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="90"/>
-      <c r="AC22" s="90"/>
-      <c r="AD22" s="90"/>
-      <c r="AE22" s="90"/>
-      <c r="AF22" s="90"/>
-      <c r="AG22" s="90"/>
-      <c r="AH22" s="90"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="91"/>
+      <c r="R22" s="91"/>
+      <c r="S22" s="91"/>
+      <c r="T22" s="91"/>
+      <c r="U22" s="91"/>
+      <c r="V22" s="91"/>
+      <c r="W22" s="91"/>
+      <c r="X22" s="91"/>
+      <c r="Y22" s="91"/>
+      <c r="Z22" s="91"/>
+      <c r="AA22" s="91"/>
+      <c r="AB22" s="91"/>
+      <c r="AC22" s="91"/>
+      <c r="AD22" s="91"/>
+      <c r="AE22" s="91"/>
+      <c r="AF22" s="91"/>
+      <c r="AG22" s="91"/>
+      <c r="AH22" s="91"/>
     </row>
     <row r="23" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A23" s="91"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="64"/>
-      <c r="W23" s="64"/>
-      <c r="X23" s="64"/>
-      <c r="Y23" s="64"/>
-      <c r="Z23" s="64"/>
-      <c r="AA23" s="64"/>
-      <c r="AB23" s="64"/>
-      <c r="AC23" s="64"/>
-      <c r="AD23" s="64"/>
-      <c r="AE23" s="64"/>
-      <c r="AF23" s="64"/>
-      <c r="AG23" s="64"/>
-      <c r="AH23" s="64"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="65"/>
+      <c r="AF23" s="65"/>
+      <c r="AG23" s="65"/>
+      <c r="AH23" s="65"/>
     </row>
     <row r="24" customHeight="1" spans="1:34">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="92" t="s">
+      <c r="B24" s="94"/>
+      <c r="C24" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="104" t="s">
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="104" t="s">
+      <c r="L24" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="M24" s="104" t="s">
+      <c r="M24" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="N24" s="92" t="s">
+      <c r="N24" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="94"/>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="94"/>
-      <c r="S24" s="94"/>
-      <c r="T24" s="94"/>
-      <c r="U24" s="94"/>
-      <c r="V24" s="94"/>
-      <c r="W24" s="94"/>
-      <c r="X24" s="94"/>
-      <c r="Y24" s="94"/>
-      <c r="Z24" s="94"/>
-      <c r="AA24" s="94"/>
-      <c r="AB24" s="94"/>
-      <c r="AC24" s="94"/>
-      <c r="AD24" s="94"/>
-      <c r="AE24" s="94"/>
-      <c r="AF24" s="94"/>
-      <c r="AG24" s="94"/>
-      <c r="AH24" s="94"/>
+      <c r="O24" s="106" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" s="106"/>
+      <c r="Q24" s="106"/>
+      <c r="R24" s="106"/>
+      <c r="S24" s="106"/>
+      <c r="T24" s="106"/>
+      <c r="U24" s="106"/>
+      <c r="V24" s="106"/>
+      <c r="W24" s="106"/>
+      <c r="X24" s="106"/>
+      <c r="Y24" s="106"/>
+      <c r="Z24" s="106"/>
+      <c r="AA24" s="106"/>
+      <c r="AB24" s="106"/>
+      <c r="AC24" s="106"/>
+      <c r="AD24" s="106"/>
+      <c r="AE24" s="106"/>
+      <c r="AF24" s="106"/>
+      <c r="AG24" s="106"/>
+      <c r="AH24" s="106"/>
     </row>
     <row r="25" customHeight="1" spans="1:34">
-      <c r="A25" s="95">
+      <c r="A25" s="96">
         <v>1</v>
       </c>
-      <c r="B25" s="96"/>
-      <c r="C25" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="105" t="s">
+      <c r="B25" s="97"/>
+      <c r="C25" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="97"/>
-      <c r="O25" s="98"/>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="98"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="98"/>
-      <c r="T25" s="98"/>
-      <c r="U25" s="98"/>
-      <c r="V25" s="98"/>
-      <c r="W25" s="98"/>
-      <c r="X25" s="98"/>
-      <c r="Y25" s="98"/>
-      <c r="Z25" s="98"/>
-      <c r="AA25" s="98"/>
-      <c r="AB25" s="98"/>
-      <c r="AC25" s="98"/>
-      <c r="AD25" s="98"/>
-      <c r="AE25" s="98"/>
-      <c r="AF25" s="98"/>
-      <c r="AG25" s="98"/>
-      <c r="AH25" s="98"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25" s="107"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="108"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="109"/>
+      <c r="S25" s="109"/>
+      <c r="T25" s="109"/>
+      <c r="U25" s="109"/>
+      <c r="V25" s="109"/>
+      <c r="W25" s="109"/>
+      <c r="X25" s="109"/>
+      <c r="Y25" s="109"/>
+      <c r="Z25" s="109"/>
+      <c r="AA25" s="109"/>
+      <c r="AB25" s="109"/>
+      <c r="AC25" s="109"/>
+      <c r="AD25" s="109"/>
+      <c r="AE25" s="109"/>
+      <c r="AF25" s="109"/>
+      <c r="AG25" s="109"/>
+      <c r="AH25" s="109"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="H5:AH5"/>
     <mergeCell ref="A6:G6"/>
@@ -3792,8 +3812,9 @@
     <mergeCell ref="A11:AH11"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C24:J24"/>
-    <mergeCell ref="N24:AH24"/>
+    <mergeCell ref="O24:AH24"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="O25:AH25"/>
     <mergeCell ref="V3:X4"/>
     <mergeCell ref="AC3:AE4"/>
     <mergeCell ref="AF3:AH4"/>
@@ -3838,7 +3859,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:25">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3854,7 +3875,7 @@
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
       <c r="M1" s="35"/>
-      <c r="N1" s="65"/>
+      <c r="N1" s="66"/>
       <c r="O1" s="36" t="s">
         <v>10</v>
       </c>
@@ -3862,20 +3883,20 @@
       <c r="Q1" s="37"/>
       <c r="R1" s="37"/>
       <c r="S1" s="37"/>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="45" t="s">
+      <c r="U1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="46"/>
-      <c r="W1" s="47" t="s">
+      <c r="V1" s="48"/>
+      <c r="W1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="117" t="s">
+      <c r="X1" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="74"/>
+      <c r="Y1" s="75"/>
     </row>
     <row r="2" customHeight="1" spans="1:25">
       <c r="A2" s="7"/>
@@ -3891,18 +3912,18 @@
       <c r="K2" s="39"/>
       <c r="L2" s="39"/>
       <c r="M2" s="39"/>
-      <c r="N2" s="66"/>
+      <c r="N2" s="67"/>
       <c r="O2" s="40"/>
       <c r="P2" s="41"/>
       <c r="Q2" s="41"/>
       <c r="R2" s="41"/>
       <c r="S2" s="41"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="75"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="76"/>
     </row>
     <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="7"/>
@@ -3920,7 +3941,7 @@
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
       <c r="M3" s="35"/>
-      <c r="N3" s="65"/>
+      <c r="N3" s="66"/>
       <c r="O3" s="36" t="s">
         <v>14</v>
       </c>
@@ -3928,20 +3949,20 @@
       <c r="Q3" s="37"/>
       <c r="R3" s="37"/>
       <c r="S3" s="37"/>
-      <c r="T3" s="44" t="s">
+      <c r="T3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="45" t="s">
+      <c r="U3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="46"/>
-      <c r="W3" s="44" t="s">
+      <c r="V3" s="48"/>
+      <c r="W3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="117" t="s">
+      <c r="X3" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="74"/>
+      <c r="Y3" s="75"/>
     </row>
     <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="9"/>
@@ -3957,22 +3978,22 @@
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
       <c r="M4" s="39"/>
-      <c r="N4" s="66"/>
+      <c r="N4" s="67"/>
       <c r="O4" s="40"/>
       <c r="P4" s="41"/>
       <c r="Q4" s="41"/>
       <c r="R4" s="41"/>
       <c r="S4" s="41"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="75"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="76"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -3985,7 +4006,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -3999,81 +4020,81 @@
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
       <c r="T5" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="V5" s="55"/>
+      <c r="V5" s="57"/>
       <c r="W5" s="12"/>
       <c r="X5" s="12"/>
       <c r="Y5" s="12"/>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A6" s="61" t="s">
-        <v>43</v>
+      <c r="A6" s="63" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="23" customHeight="1" spans="1:25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="67" t="s">
+      <c r="B7" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="68" t="s">
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="44" t="s">
+      <c r="K7" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44" t="s">
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="T7" s="44"/>
-      <c r="U7" s="68" t="s">
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="V7" s="69"/>
-      <c r="W7" s="69"/>
-      <c r="X7" s="69"/>
-      <c r="Y7" s="69"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="V7" s="70"/>
+      <c r="W7" s="70"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="70"/>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="A8" s="18">
         <v>1</v>
       </c>
-      <c r="B8" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62" t="s">
+      <c r="B8" s="43" t="s">
         <v>51</v>
       </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43" t="s">
+        <v>52</v>
+      </c>
       <c r="K8" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
@@ -4085,11 +4106,11 @@
       <c r="Q8" s="18"/>
       <c r="R8" s="18"/>
       <c r="S8" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T8" s="18"/>
       <c r="U8" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V8" s="25"/>
       <c r="W8" s="25"/>
@@ -4097,137 +4118,137 @@
       <c r="Y8" s="25"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="63"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A10" s="61" t="s">
-        <v>55</v>
+      <c r="A10" s="63" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="28" customHeight="1" spans="1:25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44" t="s">
+      <c r="B11" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44" t="s">
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="67" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="67"/>
-      <c r="S11" s="67"/>
-      <c r="T11" s="67"/>
-      <c r="U11" s="44" t="s">
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="68" t="s">
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="Y11" s="69"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y11" s="70"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A12" s="18">
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
       <c r="K12" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="33"/>
-      <c r="O12" s="71" t="s">
-        <v>51</v>
-      </c>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="118" t="s">
-        <v>60</v>
+      <c r="O12" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="122" t="s">
+        <v>61</v>
       </c>
       <c r="R12" s="18"/>
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
-      <c r="U12" s="73" t="s">
-        <v>63</v>
+      <c r="U12" s="74" t="s">
+        <v>64</v>
       </c>
       <c r="V12" s="18"/>
       <c r="W12" s="18"/>
       <c r="X12" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y12" s="76"/>
+        <v>65</v>
+      </c>
+      <c r="Y12" s="77"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A13" s="18">
         <v>2</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
       <c r="K13" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="33"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="118" t="s">
-        <v>67</v>
+      <c r="O13" s="72"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="122" t="s">
+        <v>68</v>
       </c>
       <c r="R13" s="18"/>
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
-      <c r="U13" s="73" t="s">
-        <v>63</v>
+      <c r="U13" s="74" t="s">
+        <v>64</v>
       </c>
       <c r="V13" s="18"/>
       <c r="W13" s="18"/>
       <c r="X13" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y13" s="18"/>
     </row>
@@ -4236,80 +4257,80 @@
         <v>3</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
       <c r="K14" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="33"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="118" t="s">
-        <v>67</v>
+      <c r="O14" s="72"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="122" t="s">
+        <v>68</v>
       </c>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
-      <c r="U14" s="73" t="s">
-        <v>63</v>
+      <c r="U14" s="74" t="s">
+        <v>64</v>
       </c>
       <c r="V14" s="18"/>
       <c r="W14" s="18"/>
       <c r="X14" s="27">
         <v>1</v>
       </c>
-      <c r="Y14" s="77"/>
+      <c r="Y14" s="78"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A15" s="18">
         <v>4</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
       <c r="K15" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="33"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="73"/>
       <c r="Q15" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V15" s="18"/>
       <c r="W15" s="18"/>
       <c r="X15" s="26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y15" s="33"/>
     </row>
@@ -4318,34 +4339,34 @@
         <v>5</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
       <c r="K16" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="33"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="118" t="s">
-        <v>77</v>
+      <c r="O16" s="72"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="122" t="s">
+        <v>78</v>
       </c>
       <c r="R16" s="18"/>
       <c r="S16" s="18"/>
       <c r="T16" s="18"/>
       <c r="U16" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V16" s="18"/>
       <c r="W16" s="18"/>
@@ -4359,34 +4380,34 @@
         <v>6</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="33"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="118" t="s">
-        <v>81</v>
+      <c r="O17" s="72"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="122" t="s">
+        <v>82</v>
       </c>
       <c r="R17" s="18"/>
       <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V17" s="18"/>
       <c r="W17" s="18"/>
@@ -4395,35 +4416,35 @@
       </c>
       <c r="Y17" s="33"/>
     </row>
-    <row r="18" s="60" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A18" s="63"/>
+    <row r="18" s="62" customFormat="1" customHeight="1" spans="1:1">
+      <c r="A18" s="64"/>
     </row>
     <row r="19" customHeight="1" spans="1:25">
-      <c r="A19" s="64"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="64"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="64"/>
-      <c r="R19" s="64"/>
-      <c r="S19" s="64"/>
-      <c r="T19" s="64"/>
-      <c r="U19" s="64"/>
-      <c r="V19" s="64"/>
-      <c r="W19" s="64"/>
-      <c r="X19" s="64"/>
-      <c r="Y19" s="64"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -4536,7 +4557,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:22">
       <c r="A1" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4557,20 +4578,20 @@
       <c r="N1" s="37"/>
       <c r="O1" s="37"/>
       <c r="P1" s="37"/>
-      <c r="Q1" s="44" t="s">
+      <c r="Q1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="45" t="s">
+      <c r="R1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="46"/>
-      <c r="T1" s="47" t="s">
+      <c r="S1" s="48"/>
+      <c r="T1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="117" t="s">
+      <c r="U1" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="49"/>
+      <c r="V1" s="51"/>
     </row>
     <row r="2" customHeight="1" spans="1:22">
       <c r="A2" s="7"/>
@@ -4589,12 +4610,12 @@
       <c r="N2" s="41"/>
       <c r="O2" s="41"/>
       <c r="P2" s="41"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="54"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="3" customHeight="1" spans="1:22">
       <c r="A3" s="7"/>
@@ -4617,20 +4638,20 @@
       <c r="N3" s="37"/>
       <c r="O3" s="37"/>
       <c r="P3" s="37"/>
-      <c r="Q3" s="44" t="s">
+      <c r="Q3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="45" t="s">
+      <c r="R3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="46"/>
-      <c r="T3" s="44" t="s">
+      <c r="S3" s="48"/>
+      <c r="T3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="117" t="s">
+      <c r="U3" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="49"/>
+      <c r="V3" s="51"/>
     </row>
     <row r="4" customHeight="1" spans="1:22">
       <c r="A4" s="9"/>
@@ -4649,16 +4670,16 @@
       <c r="N4" s="41"/>
       <c r="O4" s="41"/>
       <c r="P4" s="41"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="53"/>
-      <c r="V4" s="54"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="56"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4670,7 +4691,7 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -4682,12 +4703,12 @@
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="55"/>
+      <c r="S5" s="57"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
@@ -4718,7 +4739,7 @@
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:22">
       <c r="A7" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -4740,14 +4761,14 @@
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
-      <c r="V7" s="56"/>
+      <c r="V7" s="58"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:22">
       <c r="A8" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -4756,34 +4777,34 @@
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q8" s="42"/>
       <c r="R8" s="42"/>
       <c r="S8" s="42"/>
-      <c r="T8" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="U8" s="57"/>
-      <c r="V8" s="58"/>
+      <c r="T8" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="U8" s="59"/>
+      <c r="V8" s="60"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A9" s="18">
         <v>1</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -4792,24 +4813,24 @@
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
       <c r="I9" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
       <c r="L9" s="18"/>
-      <c r="M9" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="118" t="s">
-        <v>87</v>
+      <c r="M9" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="122" t="s">
+        <v>88</v>
       </c>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
       <c r="S9" s="18"/>
       <c r="T9" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
@@ -4819,7 +4840,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="20"/>
@@ -4828,24 +4849,24 @@
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
       <c r="I10" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
-      <c r="M10" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="118" t="s">
-        <v>90</v>
+      <c r="M10" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="122" t="s">
+        <v>91</v>
       </c>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
       <c r="S10" s="18"/>
       <c r="T10" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
@@ -4856,7 +4877,7 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25"/>
@@ -4864,24 +4885,24 @@
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
-      <c r="M11" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="118" t="s">
-        <v>94</v>
+      <c r="M11" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="122" t="s">
+        <v>95</v>
       </c>
       <c r="Q11" s="18"/>
       <c r="R11" s="18"/>
       <c r="S11" s="18"/>
-      <c r="T11" s="118" t="s">
-        <v>95</v>
+      <c r="T11" s="122" t="s">
+        <v>96</v>
       </c>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
@@ -4893,31 +4914,31 @@
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="I12" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
-      <c r="M12" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="118" t="s">
-        <v>98</v>
+      <c r="M12" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="122" t="s">
+        <v>99</v>
       </c>
       <c r="Q12" s="18"/>
       <c r="R12" s="18"/>
       <c r="S12" s="18"/>
-      <c r="T12" s="118" t="s">
-        <v>95</v>
+      <c r="T12" s="122" t="s">
+        <v>96</v>
       </c>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
@@ -4930,24 +4951,24 @@
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
       <c r="E13" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="I13" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
-      <c r="M13" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="119" t="s">
-        <v>101</v>
+      <c r="M13" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="124" t="s">
+        <v>102</v>
       </c>
       <c r="Q13" s="18"/>
       <c r="R13" s="18"/>
@@ -4966,28 +4987,28 @@
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="I14" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="118" t="s">
-        <v>103</v>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="122" t="s">
+        <v>104</v>
       </c>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -5000,28 +5021,28 @@
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
       <c r="E15" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="118" t="s">
-        <v>106</v>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="122" t="s">
+        <v>107</v>
       </c>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -5034,28 +5055,28 @@
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="I16" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
       <c r="P16" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="18"/>
       <c r="T16" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
@@ -5068,22 +5089,22 @@
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
       <c r="E17" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
       <c r="I17" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="118" t="s">
-        <v>110</v>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="122" t="s">
+        <v>111</v>
       </c>
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
@@ -5102,28 +5123,28 @@
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="I18" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="118" t="s">
-        <v>112</v>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="122" t="s">
+        <v>113</v>
       </c>
       <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
       <c r="S18" s="18"/>
-      <c r="T18" s="43" t="s">
-        <v>113</v>
+      <c r="T18" s="44" t="s">
+        <v>114</v>
       </c>
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
@@ -5135,25 +5156,25 @@
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
       <c r="D19" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="26"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="I19" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
-      <c r="M19" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="118" t="s">
-        <v>115</v>
+      <c r="M19" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="122" t="s">
+        <v>116</v>
       </c>
       <c r="Q19" s="18"/>
       <c r="R19" s="18"/>
@@ -5190,7 +5211,7 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A21" s="29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -5212,14 +5233,14 @@
       <c r="S21" s="30"/>
       <c r="T21" s="30"/>
       <c r="U21" s="30"/>
-      <c r="V21" s="59"/>
+      <c r="V21" s="61"/>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A22" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -5228,34 +5249,34 @@
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
       <c r="M22" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q22" s="42"/>
       <c r="R22" s="42"/>
       <c r="S22" s="42"/>
-      <c r="T22" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="U22" s="57"/>
-      <c r="V22" s="58"/>
+      <c r="T22" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="U22" s="59"/>
+      <c r="V22" s="60"/>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="1:22">
       <c r="A23" s="18">
         <v>1</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
@@ -5264,24 +5285,24 @@
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
-      <c r="M23" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="118" t="s">
-        <v>87</v>
+      <c r="M23" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="122" t="s">
+        <v>88</v>
       </c>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
@@ -5291,7 +5312,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -5300,24 +5321,24 @@
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
       <c r="I24" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
-      <c r="M24" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-      <c r="P24" s="118" t="s">
-        <v>118</v>
+      <c r="M24" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="122" t="s">
+        <v>119</v>
       </c>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18"/>
       <c r="T24" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
@@ -5327,7 +5348,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -5336,32 +5357,36 @@
       <c r="G25" s="20"/>
       <c r="H25" s="32"/>
       <c r="I25" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
-      <c r="M25" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
+      <c r="M25" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
       <c r="P25" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18"/>
       <c r="T25" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U25" s="18"/>
       <c r="V25" s="18"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1"/>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="13:15">
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+    </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A27" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -5383,14 +5408,14 @@
       <c r="S27" s="30"/>
       <c r="T27" s="30"/>
       <c r="U27" s="30"/>
-      <c r="V27" s="59"/>
+      <c r="V27" s="61"/>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A28" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -5399,34 +5424,34 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N28" s="17"/>
       <c r="O28" s="17"/>
       <c r="P28" s="42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q28" s="42"/>
       <c r="R28" s="42"/>
       <c r="S28" s="42"/>
-      <c r="T28" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="U28" s="57"/>
-      <c r="V28" s="58"/>
+      <c r="T28" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="U28" s="59"/>
+      <c r="V28" s="60"/>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="1:22">
       <c r="A29" s="18">
         <v>1</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
@@ -5435,24 +5460,24 @@
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
       <c r="I29" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
-      <c r="M29" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="118" t="s">
-        <v>87</v>
+      <c r="M29" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="122" t="s">
+        <v>88</v>
       </c>
       <c r="Q29" s="18"/>
       <c r="R29" s="18"/>
       <c r="S29" s="18"/>
       <c r="T29" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U29" s="18"/>
       <c r="V29" s="18"/>
@@ -5462,7 +5487,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -5471,24 +5496,24 @@
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
       <c r="I30" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
-      <c r="M30" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="118" t="s">
-        <v>118</v>
+      <c r="M30" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="122" t="s">
+        <v>119</v>
       </c>
       <c r="Q30" s="18"/>
       <c r="R30" s="18"/>
       <c r="S30" s="18"/>
       <c r="T30" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="U30" s="18"/>
       <c r="V30" s="18"/>
@@ -5498,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -5507,24 +5532,24 @@
       <c r="G31" s="25"/>
       <c r="H31" s="33"/>
       <c r="I31" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
-      <c r="M31" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
+      <c r="M31" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
       <c r="P31" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="18"/>
       <c r="R31" s="18"/>
       <c r="S31" s="18"/>
-      <c r="T31" s="118" t="s">
-        <v>126</v>
+      <c r="T31" s="122" t="s">
+        <v>127</v>
       </c>
       <c r="U31" s="18"/>
       <c r="V31" s="18"/>
@@ -5534,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -5543,24 +5568,24 @@
       <c r="G32" s="25"/>
       <c r="H32" s="33"/>
       <c r="I32" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
       <c r="L32" s="18"/>
-      <c r="M32" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
+      <c r="M32" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
       <c r="P32" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="18"/>
       <c r="R32" s="18"/>
       <c r="S32" s="18"/>
       <c r="T32" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U32" s="18"/>
       <c r="V32" s="18"/>
@@ -5570,7 +5595,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -5579,24 +5604,24 @@
       <c r="G33" s="25"/>
       <c r="H33" s="33"/>
       <c r="I33" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J33" s="18"/>
       <c r="K33" s="18"/>
       <c r="L33" s="18"/>
-      <c r="M33" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
+      <c r="M33" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
       <c r="P33" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q33" s="18"/>
       <c r="R33" s="18"/>
       <c r="S33" s="18"/>
       <c r="T33" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>

--- a/docs/設計/製品在庫管理/基本設計書_製品在庫照会API .xlsx
+++ b/docs/設計/製品在庫管理/基本設計書_製品在庫照会API .xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="132">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -283,9 +283,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <r>
@@ -323,7 +320,7 @@
     <t>data</t>
   </si>
   <si>
-    <t>object</t>
+    <t>Object</t>
   </si>
   <si>
     <t>データオブジェクト</t>
@@ -335,16 +332,13 @@
     <t>items</t>
   </si>
   <si>
-    <t>array</t>
+    <t>Array</t>
   </si>
   <si>
     <t>在庫情報の配列</t>
   </si>
   <si>
     <t>stockId</t>
-  </si>
-  <si>
-    <t>integer</t>
   </si>
   <si>
     <r>
@@ -482,10 +476,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -543,28 +537,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -582,14 +554,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -604,40 +584,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -656,24 +628,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -687,8 +650,39 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -721,7 +715,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +733,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,67 +835,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,25 +853,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,37 +865,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,7 +889,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1054,26 +1048,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1093,35 +1078,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1143,6 +1110,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1156,155 +1150,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1440,9 +1434,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1631,9 +1622,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2368,7 +2356,7 @@
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.66666666666667" style="28"/>
-    <col min="2" max="2" width="5.11111111111111" style="114" customWidth="1"/>
+    <col min="2" max="2" width="5.11111111111111" style="112" customWidth="1"/>
     <col min="3" max="3" width="12.3333333333333" style="28" customWidth="1"/>
     <col min="4" max="4" width="10.3333333333333" style="28" customWidth="1"/>
     <col min="5" max="5" width="66.1111111111111" style="28" customWidth="1"/>
@@ -2381,428 +2369,428 @@
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="116" t="s">
+      <c r="E2" s="114" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="118">
+      <c r="C3" s="116">
         <v>45636</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="119" t="s">
+      <c r="E3" s="117" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="118"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="117"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="117"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="119"/>
+      <c r="B7" s="115"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="117"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
+      <c r="B8" s="115"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="117"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="117"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="117"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="117"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="117"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="119"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="117"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="117"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="117"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="117"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="117"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="117"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="117"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="117"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="117"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="117"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="117"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="117"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="117"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
+      <c r="B26" s="115"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="117"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
+      <c r="B27" s="115"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="117"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="117"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="117"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="117"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
+      <c r="B31" s="115"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="117"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
+      <c r="B32" s="115"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="117"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="117"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="117"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="117"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="117"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
+      <c r="B36" s="115"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="117"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="117"/>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
+      <c r="B38" s="115"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="117"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
+      <c r="B39" s="115"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="117"/>
-      <c r="C40" s="119"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
+      <c r="B40" s="115"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="117"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
+      <c r="B41" s="115"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="117"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="117"/>
-      <c r="C42" s="119"/>
-      <c r="D42" s="119"/>
-      <c r="E42" s="119"/>
+      <c r="B42" s="115"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="117"/>
-      <c r="C43" s="119"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="119"/>
+      <c r="B43" s="115"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="117"/>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
+      <c r="B44" s="115"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="117"/>
-      <c r="C45" s="119"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
+      <c r="B45" s="115"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="117"/>
-      <c r="C46" s="119"/>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
+      <c r="B46" s="115"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="117"/>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
+      <c r="B47" s="115"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="117"/>
-      <c r="C48" s="119"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="119"/>
+      <c r="B48" s="115"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="117"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="117"/>
-      <c r="C49" s="119"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
+      <c r="B49" s="115"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="117"/>
-      <c r="C50" s="119"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="119"/>
+      <c r="B50" s="115"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="117"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="117"/>
-      <c r="C51" s="119"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
+      <c r="B51" s="115"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="117"/>
-      <c r="C52" s="119"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
+      <c r="B52" s="115"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="117"/>
-      <c r="C53" s="119"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
+      <c r="B53" s="115"/>
+      <c r="C53" s="117"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="117"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="117"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
+      <c r="B54" s="115"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="117"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="117"/>
-      <c r="C55" s="119"/>
-      <c r="D55" s="119"/>
-      <c r="E55" s="119"/>
+      <c r="B55" s="115"/>
+      <c r="C55" s="117"/>
+      <c r="D55" s="117"/>
+      <c r="E55" s="117"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="117"/>
-      <c r="C56" s="119"/>
-      <c r="D56" s="119"/>
-      <c r="E56" s="119"/>
+      <c r="B56" s="115"/>
+      <c r="C56" s="117"/>
+      <c r="D56" s="117"/>
+      <c r="E56" s="117"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="117"/>
-      <c r="C57" s="119"/>
-      <c r="D57" s="119"/>
-      <c r="E57" s="119"/>
+      <c r="B57" s="115"/>
+      <c r="C57" s="117"/>
+      <c r="D57" s="117"/>
+      <c r="E57" s="117"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="117"/>
-      <c r="C58" s="119"/>
-      <c r="D58" s="119"/>
-      <c r="E58" s="119"/>
+      <c r="B58" s="115"/>
+      <c r="C58" s="117"/>
+      <c r="D58" s="117"/>
+      <c r="E58" s="117"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="117"/>
-      <c r="C59" s="119"/>
-      <c r="D59" s="119"/>
-      <c r="E59" s="119"/>
+      <c r="B59" s="115"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="117"/>
+      <c r="E59" s="117"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="117"/>
-      <c r="C60" s="119"/>
-      <c r="D60" s="119"/>
-      <c r="E60" s="119"/>
+      <c r="B60" s="115"/>
+      <c r="C60" s="117"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="117"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="117"/>
-      <c r="C61" s="119"/>
-      <c r="D61" s="119"/>
-      <c r="E61" s="119"/>
+      <c r="B61" s="115"/>
+      <c r="C61" s="117"/>
+      <c r="D61" s="117"/>
+      <c r="E61" s="117"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="117"/>
-      <c r="C62" s="119"/>
-      <c r="D62" s="119"/>
-      <c r="E62" s="119"/>
+      <c r="B62" s="115"/>
+      <c r="C62" s="117"/>
+      <c r="D62" s="117"/>
+      <c r="E62" s="117"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="117"/>
-      <c r="C63" s="119"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="119"/>
+      <c r="B63" s="115"/>
+      <c r="C63" s="117"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="117"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="117"/>
-      <c r="C64" s="119"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="119"/>
+      <c r="B64" s="115"/>
+      <c r="C64" s="117"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="117"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="117"/>
-      <c r="C65" s="119"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
+      <c r="B65" s="115"/>
+      <c r="C65" s="117"/>
+      <c r="D65" s="117"/>
+      <c r="E65" s="117"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="117"/>
-      <c r="C66" s="119"/>
-      <c r="D66" s="119"/>
-      <c r="E66" s="119"/>
+      <c r="B66" s="115"/>
+      <c r="C66" s="117"/>
+      <c r="D66" s="117"/>
+      <c r="E66" s="117"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="117"/>
-      <c r="C67" s="119"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="119"/>
+      <c r="B67" s="115"/>
+      <c r="C67" s="117"/>
+      <c r="D67" s="117"/>
+      <c r="E67" s="117"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="117"/>
-      <c r="C68" s="119"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="119"/>
+      <c r="B68" s="115"/>
+      <c r="C68" s="117"/>
+      <c r="D68" s="117"/>
+      <c r="E68" s="117"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="117"/>
-      <c r="C69" s="119"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="119"/>
+      <c r="B69" s="115"/>
+      <c r="C69" s="117"/>
+      <c r="D69" s="117"/>
+      <c r="E69" s="117"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2816,11 +2804,11 @@
   <dimension ref="A1:AH25"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="3.66666666666667" style="79"/>
-    <col min="21" max="21" width="5.86666666666667" style="79" customWidth="1"/>
-    <col min="22" max="33" width="3.66666666666667" style="79"/>
-    <col min="34" max="34" width="13.0148148148148" style="79" customWidth="1"/>
-    <col min="35" max="16384" width="3.66666666666667" style="79"/>
+    <col min="1" max="20" width="3.66666666666667" style="78"/>
+    <col min="21" max="21" width="5.86666666666667" style="78" customWidth="1"/>
+    <col min="22" max="33" width="3.66666666666667" style="78"/>
+    <col min="34" max="34" width="13.0148148148148" style="78" customWidth="1"/>
+    <col min="35" max="16384" width="3.66666666666667" style="78"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:34">
@@ -2836,14 +2824,14 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="100"/>
+      <c r="K1" s="99"/>
       <c r="L1" s="34" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="35"/>
       <c r="N1" s="35"/>
       <c r="O1" s="35"/>
-      <c r="P1" s="66"/>
+      <c r="P1" s="65"/>
       <c r="Q1" s="36" t="s">
         <v>10</v>
       </c>
@@ -2851,27 +2839,27 @@
       <c r="S1" s="37"/>
       <c r="T1" s="37"/>
       <c r="U1" s="37"/>
-      <c r="V1" s="46" t="s">
+      <c r="V1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="47" t="s">
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="110"/>
-      <c r="AC1" s="49" t="s">
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="121" t="s">
+      <c r="AD1" s="109"/>
+      <c r="AE1" s="110"/>
+      <c r="AF1" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="75"/>
-      <c r="AH1" s="75"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
     </row>
     <row r="2" customHeight="1" spans="1:34">
       <c r="A2" s="7"/>
@@ -2884,30 +2872,30 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="101"/>
+      <c r="K2" s="100"/>
       <c r="L2" s="38"/>
       <c r="M2" s="39"/>
       <c r="N2" s="39"/>
       <c r="O2" s="39"/>
-      <c r="P2" s="67"/>
+      <c r="P2" s="66"/>
       <c r="Q2" s="40"/>
       <c r="R2" s="41"/>
       <c r="S2" s="41"/>
       <c r="T2" s="41"/>
       <c r="U2" s="41"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="54"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="76"/>
-      <c r="AH2" s="76"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="111"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="58"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="75"/>
+      <c r="AH2" s="75"/>
     </row>
     <row r="3" customHeight="1" spans="1:34">
       <c r="A3" s="7"/>
@@ -2920,14 +2908,14 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="101"/>
+      <c r="K3" s="100"/>
       <c r="L3" s="34" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="35"/>
       <c r="N3" s="35"/>
       <c r="O3" s="35"/>
-      <c r="P3" s="66"/>
+      <c r="P3" s="65"/>
       <c r="Q3" s="36" t="s">
         <v>14</v>
       </c>
@@ -2935,27 +2923,27 @@
       <c r="S3" s="37"/>
       <c r="T3" s="37"/>
       <c r="U3" s="37"/>
-      <c r="V3" s="46" t="s">
+      <c r="V3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="47" t="s">
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="110"/>
-      <c r="AC3" s="46" t="s">
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="46"/>
-      <c r="AE3" s="46"/>
-      <c r="AF3" s="121" t="s">
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="75"/>
-      <c r="AH3" s="75"/>
+      <c r="AG3" s="74"/>
+      <c r="AH3" s="74"/>
     </row>
     <row r="4" customHeight="1" spans="1:34">
       <c r="A4" s="9"/>
@@ -2968,832 +2956,832 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
-      <c r="K4" s="102"/>
+      <c r="K4" s="101"/>
       <c r="L4" s="38"/>
       <c r="M4" s="39"/>
       <c r="N4" s="39"/>
       <c r="O4" s="39"/>
-      <c r="P4" s="67"/>
+      <c r="P4" s="66"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="41"/>
       <c r="S4" s="41"/>
       <c r="T4" s="41"/>
       <c r="U4" s="41"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="53"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="46"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="76"/>
-      <c r="AH4" s="76"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="45"/>
+      <c r="AD4" s="45"/>
+      <c r="AE4" s="45"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="75"/>
+      <c r="AH4" s="75"/>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="83" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103"/>
-      <c r="AD5" s="103"/>
-      <c r="AE5" s="103"/>
-      <c r="AF5" s="103"/>
-      <c r="AG5" s="103"/>
-      <c r="AH5" s="103"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="102"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="102"/>
+      <c r="AE5" s="102"/>
+      <c r="AF5" s="102"/>
+      <c r="AG5" s="102"/>
+      <c r="AH5" s="102"/>
     </row>
     <row r="6" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="83" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="103"/>
-      <c r="S6" s="103"/>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
-      <c r="V6" s="103"/>
-      <c r="W6" s="103"/>
-      <c r="X6" s="103"/>
-      <c r="Y6" s="103"/>
-      <c r="Z6" s="103"/>
-      <c r="AA6" s="103"/>
-      <c r="AB6" s="103"/>
-      <c r="AC6" s="103"/>
-      <c r="AD6" s="103"/>
-      <c r="AE6" s="103"/>
-      <c r="AF6" s="103"/>
-      <c r="AG6" s="103"/>
-      <c r="AH6" s="103"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="102"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="102"/>
+      <c r="S6" s="102"/>
+      <c r="T6" s="102"/>
+      <c r="U6" s="102"/>
+      <c r="V6" s="102"/>
+      <c r="W6" s="102"/>
+      <c r="X6" s="102"/>
+      <c r="Y6" s="102"/>
+      <c r="Z6" s="102"/>
+      <c r="AA6" s="102"/>
+      <c r="AB6" s="102"/>
+      <c r="AC6" s="102"/>
+      <c r="AD6" s="102"/>
+      <c r="AE6" s="102"/>
+      <c r="AF6" s="102"/>
+      <c r="AG6" s="102"/>
+      <c r="AH6" s="102"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="83" t="s">
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="103"/>
-      <c r="W7" s="103"/>
-      <c r="X7" s="103"/>
-      <c r="Y7" s="103"/>
-      <c r="Z7" s="103"/>
-      <c r="AA7" s="103"/>
-      <c r="AB7" s="103"/>
-      <c r="AC7" s="103"/>
-      <c r="AD7" s="103"/>
-      <c r="AE7" s="103"/>
-      <c r="AF7" s="103"/>
-      <c r="AG7" s="103"/>
-      <c r="AH7" s="103"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="102"/>
+      <c r="U7" s="102"/>
+      <c r="V7" s="102"/>
+      <c r="W7" s="102"/>
+      <c r="X7" s="102"/>
+      <c r="Y7" s="102"/>
+      <c r="Z7" s="102"/>
+      <c r="AA7" s="102"/>
+      <c r="AB7" s="102"/>
+      <c r="AC7" s="102"/>
+      <c r="AD7" s="102"/>
+      <c r="AE7" s="102"/>
+      <c r="AF7" s="102"/>
+      <c r="AG7" s="102"/>
+      <c r="AH7" s="102"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="83" t="s">
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="103"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="103"/>
-      <c r="L8" s="103"/>
-      <c r="M8" s="103"/>
-      <c r="N8" s="103"/>
-      <c r="O8" s="103"/>
-      <c r="P8" s="103"/>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="103"/>
-      <c r="S8" s="103"/>
-      <c r="T8" s="103"/>
-      <c r="U8" s="103"/>
-      <c r="V8" s="103"/>
-      <c r="W8" s="103"/>
-      <c r="X8" s="103"/>
-      <c r="Y8" s="103"/>
-      <c r="Z8" s="103"/>
-      <c r="AA8" s="103"/>
-      <c r="AB8" s="103"/>
-      <c r="AC8" s="103"/>
-      <c r="AD8" s="103"/>
-      <c r="AE8" s="103"/>
-      <c r="AF8" s="103"/>
-      <c r="AG8" s="103"/>
-      <c r="AH8" s="103"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="102"/>
+      <c r="N8" s="102"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="102"/>
+      <c r="Q8" s="102"/>
+      <c r="R8" s="102"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="102"/>
+      <c r="AD8" s="102"/>
+      <c r="AE8" s="102"/>
+      <c r="AF8" s="102"/>
+      <c r="AG8" s="102"/>
+      <c r="AH8" s="102"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="81"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="83" t="s">
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="103"/>
-      <c r="AB9" s="103"/>
-      <c r="AC9" s="103"/>
-      <c r="AD9" s="103"/>
-      <c r="AE9" s="103"/>
-      <c r="AF9" s="103"/>
-      <c r="AG9" s="103"/>
-      <c r="AH9" s="103"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="102"/>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="102"/>
+      <c r="S9" s="102"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="102"/>
+      <c r="V9" s="102"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="102"/>
+      <c r="Y9" s="102"/>
+      <c r="Z9" s="102"/>
+      <c r="AA9" s="102"/>
+      <c r="AB9" s="102"/>
+      <c r="AC9" s="102"/>
+      <c r="AD9" s="102"/>
+      <c r="AE9" s="102"/>
+      <c r="AF9" s="102"/>
+      <c r="AG9" s="102"/>
+      <c r="AH9" s="102"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="87" t="s">
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="104"/>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="104"/>
-      <c r="S10" s="104"/>
-      <c r="T10" s="104"/>
-      <c r="U10" s="104"/>
-      <c r="V10" s="104"/>
-      <c r="W10" s="104"/>
-      <c r="X10" s="104"/>
-      <c r="Y10" s="104"/>
-      <c r="Z10" s="104"/>
-      <c r="AA10" s="104"/>
-      <c r="AB10" s="104"/>
-      <c r="AC10" s="104"/>
-      <c r="AD10" s="104"/>
-      <c r="AE10" s="104"/>
-      <c r="AF10" s="104"/>
-      <c r="AG10" s="104"/>
-      <c r="AH10" s="104"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="103"/>
+      <c r="K10" s="103"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="103"/>
+      <c r="P10" s="103"/>
+      <c r="Q10" s="103"/>
+      <c r="R10" s="103"/>
+      <c r="S10" s="103"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
+      <c r="Y10" s="103"/>
+      <c r="Z10" s="103"/>
+      <c r="AA10" s="103"/>
+      <c r="AB10" s="103"/>
+      <c r="AC10" s="103"/>
+      <c r="AD10" s="103"/>
+      <c r="AE10" s="103"/>
+      <c r="AF10" s="103"/>
+      <c r="AG10" s="103"/>
+      <c r="AH10" s="103"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="89"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="89"/>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
-      <c r="M11" s="89"/>
-      <c r="N11" s="89"/>
-      <c r="O11" s="89"/>
-      <c r="P11" s="89"/>
-      <c r="Q11" s="89"/>
-      <c r="R11" s="89"/>
-      <c r="S11" s="89"/>
-      <c r="T11" s="89"/>
-      <c r="U11" s="89"/>
-      <c r="V11" s="89"/>
-      <c r="W11" s="89"/>
-      <c r="X11" s="89"/>
-      <c r="Y11" s="89"/>
-      <c r="Z11" s="89"/>
-      <c r="AA11" s="89"/>
-      <c r="AB11" s="89"/>
-      <c r="AC11" s="89"/>
-      <c r="AD11" s="89"/>
-      <c r="AE11" s="89"/>
-      <c r="AF11" s="89"/>
-      <c r="AG11" s="89"/>
-      <c r="AH11" s="89"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="88"/>
+      <c r="AF11" s="88"/>
+      <c r="AG11" s="88"/>
+      <c r="AH11" s="88"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
-      <c r="Q12" s="91"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="91"/>
-      <c r="T12" s="91"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="91"/>
-      <c r="Y12" s="91"/>
-      <c r="Z12" s="91"/>
-      <c r="AA12" s="91"/>
-      <c r="AB12" s="91"/>
-      <c r="AC12" s="91"/>
-      <c r="AD12" s="91"/>
-      <c r="AE12" s="91"/>
-      <c r="AF12" s="91"/>
-      <c r="AG12" s="91"/>
-      <c r="AH12" s="91"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="90"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="90"/>
+      <c r="W12" s="90"/>
+      <c r="X12" s="90"/>
+      <c r="Y12" s="90"/>
+      <c r="Z12" s="90"/>
+      <c r="AA12" s="90"/>
+      <c r="AB12" s="90"/>
+      <c r="AC12" s="90"/>
+      <c r="AD12" s="90"/>
+      <c r="AE12" s="90"/>
+      <c r="AF12" s="90"/>
+      <c r="AG12" s="90"/>
+      <c r="AH12" s="90"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="91"/>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="91"/>
-      <c r="S13" s="91"/>
-      <c r="T13" s="91"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="91"/>
-      <c r="W13" s="91"/>
-      <c r="X13" s="91"/>
-      <c r="Y13" s="91"/>
-      <c r="Z13" s="91"/>
-      <c r="AA13" s="91"/>
-      <c r="AB13" s="91"/>
-      <c r="AC13" s="91"/>
-      <c r="AD13" s="91"/>
-      <c r="AE13" s="91"/>
-      <c r="AF13" s="91"/>
-      <c r="AG13" s="91"/>
-      <c r="AH13" s="91"/>
+      <c r="A13" s="89"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="90"/>
+      <c r="W13" s="90"/>
+      <c r="X13" s="90"/>
+      <c r="Y13" s="90"/>
+      <c r="Z13" s="90"/>
+      <c r="AA13" s="90"/>
+      <c r="AB13" s="90"/>
+      <c r="AC13" s="90"/>
+      <c r="AD13" s="90"/>
+      <c r="AE13" s="90"/>
+      <c r="AF13" s="90"/>
+      <c r="AG13" s="90"/>
+      <c r="AH13" s="90"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A14" s="90"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="91"/>
-      <c r="S14" s="91"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="91"/>
-      <c r="V14" s="91"/>
-      <c r="W14" s="91"/>
-      <c r="X14" s="91"/>
-      <c r="Y14" s="91"/>
-      <c r="Z14" s="91"/>
-      <c r="AA14" s="91"/>
-      <c r="AB14" s="91"/>
-      <c r="AC14" s="91"/>
-      <c r="AD14" s="91"/>
-      <c r="AE14" s="91"/>
-      <c r="AF14" s="91"/>
-      <c r="AG14" s="91"/>
-      <c r="AH14" s="91"/>
+      <c r="A14" s="89"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="90"/>
+      <c r="P14" s="90"/>
+      <c r="Q14" s="90"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="90"/>
+      <c r="U14" s="90"/>
+      <c r="V14" s="90"/>
+      <c r="W14" s="90"/>
+      <c r="X14" s="90"/>
+      <c r="Y14" s="90"/>
+      <c r="Z14" s="90"/>
+      <c r="AA14" s="90"/>
+      <c r="AB14" s="90"/>
+      <c r="AC14" s="90"/>
+      <c r="AD14" s="90"/>
+      <c r="AE14" s="90"/>
+      <c r="AF14" s="90"/>
+      <c r="AG14" s="90"/>
+      <c r="AH14" s="90"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A15" s="90"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
-      <c r="T15" s="91"/>
-      <c r="U15" s="91"/>
-      <c r="V15" s="91"/>
-      <c r="W15" s="91"/>
-      <c r="X15" s="91"/>
-      <c r="Y15" s="91"/>
-      <c r="Z15" s="91"/>
-      <c r="AA15" s="91"/>
-      <c r="AB15" s="91"/>
-      <c r="AC15" s="91"/>
-      <c r="AD15" s="91"/>
-      <c r="AE15" s="91"/>
-      <c r="AF15" s="91"/>
-      <c r="AG15" s="91"/>
-      <c r="AH15" s="91"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="90"/>
+      <c r="N15" s="90"/>
+      <c r="O15" s="90"/>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="90"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="90"/>
+      <c r="T15" s="90"/>
+      <c r="U15" s="90"/>
+      <c r="V15" s="90"/>
+      <c r="W15" s="90"/>
+      <c r="X15" s="90"/>
+      <c r="Y15" s="90"/>
+      <c r="Z15" s="90"/>
+      <c r="AA15" s="90"/>
+      <c r="AB15" s="90"/>
+      <c r="AC15" s="90"/>
+      <c r="AD15" s="90"/>
+      <c r="AE15" s="90"/>
+      <c r="AF15" s="90"/>
+      <c r="AG15" s="90"/>
+      <c r="AH15" s="90"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A16" s="90"/>
-      <c r="B16" s="91"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="91"/>
-      <c r="S16" s="91"/>
-      <c r="T16" s="91"/>
-      <c r="U16" s="91"/>
-      <c r="V16" s="91"/>
-      <c r="W16" s="91"/>
-      <c r="X16" s="91"/>
-      <c r="Y16" s="91"/>
-      <c r="Z16" s="91"/>
-      <c r="AA16" s="91"/>
-      <c r="AB16" s="91"/>
-      <c r="AC16" s="91"/>
-      <c r="AD16" s="91"/>
-      <c r="AE16" s="91"/>
-      <c r="AF16" s="91"/>
-      <c r="AG16" s="91"/>
-      <c r="AH16" s="91"/>
+      <c r="A16" s="89"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="90"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="90"/>
+      <c r="U16" s="90"/>
+      <c r="V16" s="90"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="90"/>
+      <c r="Y16" s="90"/>
+      <c r="Z16" s="90"/>
+      <c r="AA16" s="90"/>
+      <c r="AB16" s="90"/>
+      <c r="AC16" s="90"/>
+      <c r="AD16" s="90"/>
+      <c r="AE16" s="90"/>
+      <c r="AF16" s="90"/>
+      <c r="AG16" s="90"/>
+      <c r="AH16" s="90"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A17" s="90"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="91"/>
-      <c r="W17" s="91"/>
-      <c r="X17" s="91"/>
-      <c r="Y17" s="91"/>
-      <c r="Z17" s="91"/>
-      <c r="AA17" s="91"/>
-      <c r="AB17" s="91"/>
-      <c r="AC17" s="91"/>
-      <c r="AD17" s="91"/>
-      <c r="AE17" s="91"/>
-      <c r="AF17" s="91"/>
-      <c r="AG17" s="91"/>
-      <c r="AH17" s="91"/>
+      <c r="A17" s="89"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="90"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="90"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="90"/>
+      <c r="T17" s="90"/>
+      <c r="U17" s="90"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="90"/>
+      <c r="X17" s="90"/>
+      <c r="Y17" s="90"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="90"/>
+      <c r="AB17" s="90"/>
+      <c r="AC17" s="90"/>
+      <c r="AD17" s="90"/>
+      <c r="AE17" s="90"/>
+      <c r="AF17" s="90"/>
+      <c r="AG17" s="90"/>
+      <c r="AH17" s="90"/>
     </row>
     <row r="18" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A18" s="90"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="91"/>
-      <c r="T18" s="91"/>
-      <c r="U18" s="91"/>
-      <c r="V18" s="91"/>
-      <c r="W18" s="91"/>
-      <c r="X18" s="91"/>
-      <c r="Y18" s="91"/>
-      <c r="Z18" s="91"/>
-      <c r="AA18" s="91"/>
-      <c r="AB18" s="91"/>
-      <c r="AC18" s="91"/>
-      <c r="AD18" s="91"/>
-      <c r="AE18" s="91"/>
-      <c r="AF18" s="91"/>
-      <c r="AG18" s="91"/>
-      <c r="AH18" s="91"/>
+      <c r="A18" s="89"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
     </row>
     <row r="19" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="91"/>
-      <c r="R19" s="91"/>
-      <c r="S19" s="91"/>
-      <c r="T19" s="91"/>
-      <c r="U19" s="91"/>
-      <c r="V19" s="91"/>
-      <c r="W19" s="91"/>
-      <c r="X19" s="91"/>
-      <c r="Y19" s="91"/>
-      <c r="Z19" s="91"/>
-      <c r="AA19" s="91"/>
-      <c r="AB19" s="91"/>
-      <c r="AC19" s="91"/>
-      <c r="AD19" s="91"/>
-      <c r="AE19" s="91"/>
-      <c r="AF19" s="91"/>
-      <c r="AG19" s="91"/>
-      <c r="AH19" s="91"/>
+      <c r="A19" s="89"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="90"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="90"/>
+      <c r="T19" s="90"/>
+      <c r="U19" s="90"/>
+      <c r="V19" s="90"/>
+      <c r="W19" s="90"/>
+      <c r="X19" s="90"/>
+      <c r="Y19" s="90"/>
+      <c r="Z19" s="90"/>
+      <c r="AA19" s="90"/>
+      <c r="AB19" s="90"/>
+      <c r="AC19" s="90"/>
+      <c r="AD19" s="90"/>
+      <c r="AE19" s="90"/>
+      <c r="AF19" s="90"/>
+      <c r="AG19" s="90"/>
+      <c r="AH19" s="90"/>
     </row>
     <row r="20" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A20" s="90"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="91"/>
-      <c r="R20" s="91"/>
-      <c r="S20" s="91"/>
-      <c r="T20" s="91"/>
-      <c r="U20" s="91"/>
-      <c r="V20" s="91"/>
-      <c r="W20" s="91"/>
-      <c r="X20" s="91"/>
-      <c r="Y20" s="91"/>
-      <c r="Z20" s="91"/>
-      <c r="AA20" s="91"/>
-      <c r="AB20" s="91"/>
-      <c r="AC20" s="91"/>
-      <c r="AD20" s="91"/>
-      <c r="AE20" s="91"/>
-      <c r="AF20" s="91"/>
-      <c r="AG20" s="91"/>
-      <c r="AH20" s="91"/>
+      <c r="A20" s="89"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="90"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="90"/>
+      <c r="U20" s="90"/>
+      <c r="V20" s="90"/>
+      <c r="W20" s="90"/>
+      <c r="X20" s="90"/>
+      <c r="Y20" s="90"/>
+      <c r="Z20" s="90"/>
+      <c r="AA20" s="90"/>
+      <c r="AB20" s="90"/>
+      <c r="AC20" s="90"/>
+      <c r="AD20" s="90"/>
+      <c r="AE20" s="90"/>
+      <c r="AF20" s="90"/>
+      <c r="AG20" s="90"/>
+      <c r="AH20" s="90"/>
     </row>
     <row r="21" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A21" s="90"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="91"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="91"/>
-      <c r="Q21" s="91"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="91"/>
-      <c r="T21" s="91"/>
-      <c r="U21" s="91"/>
-      <c r="V21" s="91"/>
-      <c r="W21" s="91"/>
-      <c r="X21" s="91"/>
-      <c r="Y21" s="91"/>
-      <c r="Z21" s="91"/>
-      <c r="AA21" s="91"/>
-      <c r="AB21" s="91"/>
-      <c r="AC21" s="91"/>
-      <c r="AD21" s="91"/>
-      <c r="AE21" s="91"/>
-      <c r="AF21" s="91"/>
-      <c r="AG21" s="91"/>
-      <c r="AH21" s="91"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="90"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="90"/>
+      <c r="T21" s="90"/>
+      <c r="U21" s="90"/>
+      <c r="V21" s="90"/>
+      <c r="W21" s="90"/>
+      <c r="X21" s="90"/>
+      <c r="Y21" s="90"/>
+      <c r="Z21" s="90"/>
+      <c r="AA21" s="90"/>
+      <c r="AB21" s="90"/>
+      <c r="AC21" s="90"/>
+      <c r="AD21" s="90"/>
+      <c r="AE21" s="90"/>
+      <c r="AF21" s="90"/>
+      <c r="AG21" s="90"/>
+      <c r="AH21" s="90"/>
     </row>
     <row r="22" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A22" s="90"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="91"/>
-      <c r="R22" s="91"/>
-      <c r="S22" s="91"/>
-      <c r="T22" s="91"/>
-      <c r="U22" s="91"/>
-      <c r="V22" s="91"/>
-      <c r="W22" s="91"/>
-      <c r="X22" s="91"/>
-      <c r="Y22" s="91"/>
-      <c r="Z22" s="91"/>
-      <c r="AA22" s="91"/>
-      <c r="AB22" s="91"/>
-      <c r="AC22" s="91"/>
-      <c r="AD22" s="91"/>
-      <c r="AE22" s="91"/>
-      <c r="AF22" s="91"/>
-      <c r="AG22" s="91"/>
-      <c r="AH22" s="91"/>
+      <c r="A22" s="89"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="90"/>
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="90"/>
+      <c r="U22" s="90"/>
+      <c r="V22" s="90"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="90"/>
+      <c r="Y22" s="90"/>
+      <c r="Z22" s="90"/>
+      <c r="AA22" s="90"/>
+      <c r="AB22" s="90"/>
+      <c r="AC22" s="90"/>
+      <c r="AD22" s="90"/>
+      <c r="AE22" s="90"/>
+      <c r="AF22" s="90"/>
+      <c r="AG22" s="90"/>
+      <c r="AH22" s="90"/>
     </row>
     <row r="23" s="4" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A23" s="92"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="65"/>
-      <c r="AC23" s="65"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="65"/>
-      <c r="AF23" s="65"/>
-      <c r="AG23" s="65"/>
-      <c r="AH23" s="65"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="64"/>
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="64"/>
+      <c r="AB23" s="64"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="64"/>
+      <c r="AE23" s="64"/>
+      <c r="AF23" s="64"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
     </row>
     <row r="24" customHeight="1" spans="1:34">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="93" t="s">
+      <c r="B24" s="93"/>
+      <c r="C24" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="94"/>
-      <c r="K24" s="105" t="s">
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="105" t="s">
+      <c r="L24" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="M24" s="105" t="s">
+      <c r="M24" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="N24" s="93" t="s">
+      <c r="N24" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="106" t="s">
+      <c r="O24" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="106"/>
-      <c r="Q24" s="106"/>
-      <c r="R24" s="106"/>
-      <c r="S24" s="106"/>
-      <c r="T24" s="106"/>
-      <c r="U24" s="106"/>
-      <c r="V24" s="106"/>
-      <c r="W24" s="106"/>
-      <c r="X24" s="106"/>
-      <c r="Y24" s="106"/>
-      <c r="Z24" s="106"/>
-      <c r="AA24" s="106"/>
-      <c r="AB24" s="106"/>
-      <c r="AC24" s="106"/>
-      <c r="AD24" s="106"/>
-      <c r="AE24" s="106"/>
-      <c r="AF24" s="106"/>
-      <c r="AG24" s="106"/>
-      <c r="AH24" s="106"/>
+      <c r="P24" s="105"/>
+      <c r="Q24" s="105"/>
+      <c r="R24" s="105"/>
+      <c r="S24" s="105"/>
+      <c r="T24" s="105"/>
+      <c r="U24" s="105"/>
+      <c r="V24" s="105"/>
+      <c r="W24" s="105"/>
+      <c r="X24" s="105"/>
+      <c r="Y24" s="105"/>
+      <c r="Z24" s="105"/>
+      <c r="AA24" s="105"/>
+      <c r="AB24" s="105"/>
+      <c r="AC24" s="105"/>
+      <c r="AD24" s="105"/>
+      <c r="AE24" s="105"/>
+      <c r="AF24" s="105"/>
+      <c r="AG24" s="105"/>
+      <c r="AH24" s="105"/>
     </row>
     <row r="25" customHeight="1" spans="1:34">
-      <c r="A25" s="96">
+      <c r="A25" s="95">
         <v>1</v>
       </c>
-      <c r="B25" s="97"/>
-      <c r="C25" s="98" t="s">
+      <c r="B25" s="96"/>
+      <c r="C25" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="107" t="s">
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="98"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="107"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="108"/>
-      <c r="O25" s="109"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="109"/>
-      <c r="R25" s="109"/>
-      <c r="S25" s="109"/>
-      <c r="T25" s="109"/>
-      <c r="U25" s="109"/>
-      <c r="V25" s="109"/>
-      <c r="W25" s="109"/>
-      <c r="X25" s="109"/>
-      <c r="Y25" s="109"/>
-      <c r="Z25" s="109"/>
-      <c r="AA25" s="109"/>
-      <c r="AB25" s="109"/>
-      <c r="AC25" s="109"/>
-      <c r="AD25" s="109"/>
-      <c r="AE25" s="109"/>
-      <c r="AF25" s="109"/>
-      <c r="AG25" s="109"/>
-      <c r="AH25" s="109"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="107"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
+      <c r="Q25" s="106"/>
+      <c r="R25" s="106"/>
+      <c r="S25" s="106"/>
+      <c r="T25" s="106"/>
+      <c r="U25" s="106"/>
+      <c r="V25" s="106"/>
+      <c r="W25" s="106"/>
+      <c r="X25" s="106"/>
+      <c r="Y25" s="106"/>
+      <c r="Z25" s="106"/>
+      <c r="AA25" s="106"/>
+      <c r="AB25" s="106"/>
+      <c r="AC25" s="106"/>
+      <c r="AD25" s="106"/>
+      <c r="AE25" s="106"/>
+      <c r="AF25" s="106"/>
+      <c r="AG25" s="106"/>
+      <c r="AH25" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -3875,7 +3863,7 @@
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
       <c r="M1" s="35"/>
-      <c r="N1" s="66"/>
+      <c r="N1" s="65"/>
       <c r="O1" s="36" t="s">
         <v>10</v>
       </c>
@@ -3883,20 +3871,20 @@
       <c r="Q1" s="37"/>
       <c r="R1" s="37"/>
       <c r="S1" s="37"/>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="47" t="s">
+      <c r="U1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="48"/>
-      <c r="W1" s="49" t="s">
+      <c r="V1" s="47"/>
+      <c r="W1" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="121" t="s">
+      <c r="X1" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="75"/>
+      <c r="Y1" s="74"/>
     </row>
     <row r="2" customHeight="1" spans="1:25">
       <c r="A2" s="7"/>
@@ -3912,18 +3900,18 @@
       <c r="K2" s="39"/>
       <c r="L2" s="39"/>
       <c r="M2" s="39"/>
-      <c r="N2" s="67"/>
+      <c r="N2" s="66"/>
       <c r="O2" s="40"/>
       <c r="P2" s="41"/>
       <c r="Q2" s="41"/>
       <c r="R2" s="41"/>
       <c r="S2" s="41"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="76"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="75"/>
     </row>
     <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="7"/>
@@ -3941,7 +3929,7 @@
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
       <c r="M3" s="35"/>
-      <c r="N3" s="66"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="36" t="s">
         <v>14</v>
       </c>
@@ -3949,20 +3937,20 @@
       <c r="Q3" s="37"/>
       <c r="R3" s="37"/>
       <c r="S3" s="37"/>
-      <c r="T3" s="46" t="s">
+      <c r="T3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="47" t="s">
+      <c r="U3" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="48"/>
-      <c r="W3" s="46" t="s">
+      <c r="V3" s="47"/>
+      <c r="W3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="121" t="s">
+      <c r="X3" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="75"/>
+      <c r="Y3" s="74"/>
     </row>
     <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="9"/>
@@ -3978,18 +3966,18 @@
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
       <c r="M4" s="39"/>
-      <c r="N4" s="67"/>
+      <c r="N4" s="66"/>
       <c r="O4" s="40"/>
       <c r="P4" s="41"/>
       <c r="Q4" s="41"/>
       <c r="R4" s="41"/>
       <c r="S4" s="41"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="76"/>
+      <c r="T4" s="45"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="54"/>
+      <c r="Y4" s="75"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="11" t="s">
@@ -4025,56 +4013,56 @@
       <c r="U5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="V5" s="57"/>
+      <c r="V5" s="56"/>
       <c r="W5" s="12"/>
       <c r="X5" s="12"/>
       <c r="Y5" s="12"/>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="62" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="23" customHeight="1" spans="1:25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="68" t="s">
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="69" t="s">
+      <c r="K7" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="46" t="s">
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46" t="s">
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="T7" s="46"/>
-      <c r="U7" s="69" t="s">
+      <c r="T7" s="45"/>
+      <c r="U7" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="V7" s="70"/>
-      <c r="W7" s="70"/>
-      <c r="X7" s="70"/>
-      <c r="Y7" s="70"/>
+      <c r="V7" s="69"/>
+      <c r="W7" s="69"/>
+      <c r="X7" s="69"/>
+      <c r="Y7" s="69"/>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="A8" s="18">
@@ -4118,55 +4106,55 @@
       <c r="Y8" s="25"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A9" s="63"/>
+      <c r="A9" s="62"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="62" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="28" customHeight="1" spans="1:25">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46" t="s">
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46" t="s">
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="68" t="s">
+      <c r="P11" s="45"/>
+      <c r="Q11" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="68"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="68"/>
-      <c r="U11" s="46" t="s">
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="69" t="s">
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="Y11" s="70"/>
+      <c r="Y11" s="69"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A12" s="18">
@@ -4191,17 +4179,17 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="33"/>
-      <c r="O12" s="72" t="s">
+      <c r="O12" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="122" t="s">
+      <c r="P12" s="72"/>
+      <c r="Q12" s="120" t="s">
         <v>61</v>
       </c>
       <c r="R12" s="18"/>
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
-      <c r="U12" s="74" t="s">
+      <c r="U12" s="73" t="s">
         <v>64</v>
       </c>
       <c r="V12" s="18"/>
@@ -4209,7 +4197,7 @@
       <c r="X12" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="Y12" s="77"/>
+      <c r="Y12" s="76"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A13" s="18">
@@ -4234,15 +4222,15 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="33"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="122" t="s">
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="120" t="s">
         <v>68</v>
       </c>
       <c r="R13" s="18"/>
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
-      <c r="U13" s="74" t="s">
+      <c r="U13" s="73" t="s">
         <v>64</v>
       </c>
       <c r="V13" s="18"/>
@@ -4275,15 +4263,15 @@
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="33"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="122" t="s">
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="120" t="s">
         <v>68</v>
       </c>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
-      <c r="U14" s="74" t="s">
+      <c r="U14" s="73" t="s">
         <v>64</v>
       </c>
       <c r="V14" s="18"/>
@@ -4291,7 +4279,7 @@
       <c r="X14" s="27">
         <v>1</v>
       </c>
-      <c r="Y14" s="78"/>
+      <c r="Y14" s="77"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A15" s="18">
@@ -4316,8 +4304,8 @@
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="33"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
       <c r="Q15" s="18" t="s">
         <v>71</v>
       </c>
@@ -4357,9 +4345,9 @@
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="33"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="122" t="s">
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="120" t="s">
         <v>78</v>
       </c>
       <c r="R16" s="18"/>
@@ -4398,9 +4386,9 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="33"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="122" t="s">
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="120" t="s">
         <v>82</v>
       </c>
       <c r="R17" s="18"/>
@@ -4416,35 +4404,35 @@
       </c>
       <c r="Y17" s="33"/>
     </row>
-    <row r="18" s="62" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A18" s="64"/>
+    <row r="18" s="61" customFormat="1" customHeight="1" spans="1:1">
+      <c r="A18" s="63"/>
     </row>
     <row r="19" customHeight="1" spans="1:25">
-      <c r="A19" s="65"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="64"/>
+      <c r="S19" s="64"/>
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -4578,20 +4566,20 @@
       <c r="N1" s="37"/>
       <c r="O1" s="37"/>
       <c r="P1" s="37"/>
-      <c r="Q1" s="46" t="s">
+      <c r="Q1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="47" t="s">
+      <c r="R1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="48"/>
-      <c r="T1" s="49" t="s">
+      <c r="S1" s="47"/>
+      <c r="T1" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="121" t="s">
+      <c r="U1" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="51"/>
+      <c r="V1" s="50"/>
     </row>
     <row r="2" customHeight="1" spans="1:22">
       <c r="A2" s="7"/>
@@ -4610,12 +4598,12 @@
       <c r="N2" s="41"/>
       <c r="O2" s="41"/>
       <c r="P2" s="41"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="56"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="55"/>
     </row>
     <row r="3" customHeight="1" spans="1:22">
       <c r="A3" s="7"/>
@@ -4638,20 +4626,20 @@
       <c r="N3" s="37"/>
       <c r="O3" s="37"/>
       <c r="P3" s="37"/>
-      <c r="Q3" s="46" t="s">
+      <c r="Q3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="47" t="s">
+      <c r="R3" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="48"/>
-      <c r="T3" s="46" t="s">
+      <c r="S3" s="47"/>
+      <c r="T3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="121" t="s">
+      <c r="U3" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="51"/>
+      <c r="V3" s="50"/>
     </row>
     <row r="4" customHeight="1" spans="1:22">
       <c r="A4" s="9"/>
@@ -4670,12 +4658,12 @@
       <c r="N4" s="41"/>
       <c r="O4" s="41"/>
       <c r="P4" s="41"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="56"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="45"/>
+      <c r="U4" s="54"/>
+      <c r="V4" s="55"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="11" t="s">
@@ -4708,7 +4696,7 @@
       <c r="R5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="57"/>
+      <c r="S5" s="56"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
@@ -4761,7 +4749,7 @@
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
-      <c r="V7" s="58"/>
+      <c r="V7" s="57"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:22">
       <c r="A8" s="17" t="s">
@@ -4793,11 +4781,11 @@
       <c r="Q8" s="42"/>
       <c r="R8" s="42"/>
       <c r="S8" s="42"/>
-      <c r="T8" s="54" t="s">
+      <c r="T8" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="U8" s="59"/>
-      <c r="V8" s="60"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="59"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A9" s="18">
@@ -4812,25 +4800,25 @@
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
-      <c r="I9" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="123" t="s">
+      <c r="I9" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N9" s="43"/>
       <c r="O9" s="43"/>
-      <c r="P9" s="122" t="s">
-        <v>88</v>
+      <c r="P9" s="120" t="s">
+        <v>87</v>
       </c>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
       <c r="S9" s="18"/>
       <c r="T9" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
@@ -4840,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="20"/>
@@ -4848,25 +4836,25 @@
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="123" t="s">
+      <c r="I10" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N10" s="43"/>
       <c r="O10" s="43"/>
-      <c r="P10" s="122" t="s">
-        <v>91</v>
+      <c r="P10" s="120" t="s">
+        <v>90</v>
       </c>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
       <c r="S10" s="18"/>
       <c r="T10" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
@@ -4877,7 +4865,7 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25"/>
@@ -4885,24 +4873,24 @@
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
-      <c r="M11" s="123" t="s">
+      <c r="M11" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N11" s="43"/>
       <c r="O11" s="43"/>
-      <c r="P11" s="122" t="s">
-        <v>95</v>
+      <c r="P11" s="120" t="s">
+        <v>94</v>
       </c>
       <c r="Q11" s="18"/>
       <c r="R11" s="18"/>
       <c r="S11" s="18"/>
-      <c r="T11" s="122" t="s">
-        <v>96</v>
+      <c r="T11" s="120" t="s">
+        <v>95</v>
       </c>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
@@ -4914,31 +4902,31 @@
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
       <c r="I12" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
-      <c r="M12" s="123" t="s">
+      <c r="M12" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N12" s="43"/>
       <c r="O12" s="43"/>
-      <c r="P12" s="122" t="s">
-        <v>99</v>
+      <c r="P12" s="120" t="s">
+        <v>98</v>
       </c>
       <c r="Q12" s="18"/>
       <c r="R12" s="18"/>
       <c r="S12" s="18"/>
-      <c r="T12" s="122" t="s">
-        <v>96</v>
+      <c r="T12" s="120" t="s">
+        <v>95</v>
       </c>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
@@ -4951,24 +4939,24 @@
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
       <c r="E13" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
-      <c r="I13" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="123" t="s">
+      <c r="I13" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
-      <c r="P13" s="124" t="s">
-        <v>102</v>
+      <c r="P13" s="122" t="s">
+        <v>100</v>
       </c>
       <c r="Q13" s="18"/>
       <c r="R13" s="18"/>
@@ -4987,28 +4975,28 @@
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
-      <c r="I14" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
+      <c r="I14" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="33"/>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
-      <c r="P14" s="122" t="s">
-        <v>104</v>
+      <c r="P14" s="120" t="s">
+        <v>102</v>
       </c>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -5021,28 +5009,28 @@
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
       <c r="E15" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
-      <c r="I15" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
+      <c r="I15" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="33"/>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
-      <c r="P15" s="122" t="s">
-        <v>107</v>
+      <c r="P15" s="120" t="s">
+        <v>105</v>
       </c>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -5055,17 +5043,17 @@
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
-      <c r="I16" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
+      <c r="I16" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="33"/>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
@@ -5089,22 +5077,22 @@
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
       <c r="E17" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
-      <c r="I17" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
+      <c r="I17" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="33"/>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
       <c r="O17" s="43"/>
-      <c r="P17" s="122" t="s">
-        <v>111</v>
+      <c r="P17" s="120" t="s">
+        <v>109</v>
       </c>
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
@@ -5123,28 +5111,28 @@
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
+      <c r="I18" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="33"/>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
       <c r="O18" s="43"/>
-      <c r="P18" s="122" t="s">
-        <v>113</v>
+      <c r="P18" s="120" t="s">
+        <v>111</v>
       </c>
       <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
       <c r="S18" s="18"/>
       <c r="T18" s="44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
@@ -5156,25 +5144,25 @@
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
       <c r="D19" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="26"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="123" t="s">
+      <c r="I19" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N19" s="43"/>
       <c r="O19" s="43"/>
-      <c r="P19" s="122" t="s">
-        <v>116</v>
+      <c r="P19" s="120" t="s">
+        <v>114</v>
       </c>
       <c r="Q19" s="18"/>
       <c r="R19" s="18"/>
@@ -5211,7 +5199,7 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A21" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -5233,7 +5221,7 @@
       <c r="S21" s="30"/>
       <c r="T21" s="30"/>
       <c r="U21" s="30"/>
-      <c r="V21" s="61"/>
+      <c r="V21" s="60"/>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A22" s="17" t="s">
@@ -5265,18 +5253,18 @@
       <c r="Q22" s="42"/>
       <c r="R22" s="42"/>
       <c r="S22" s="42"/>
-      <c r="T22" s="54" t="s">
+      <c r="T22" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="U22" s="59"/>
-      <c r="V22" s="60"/>
+      <c r="U22" s="58"/>
+      <c r="V22" s="59"/>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="1:22">
       <c r="A23" s="18">
         <v>1</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
@@ -5284,25 +5272,25 @@
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
-      <c r="I23" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="123" t="s">
+      <c r="I23" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N23" s="43"/>
       <c r="O23" s="43"/>
-      <c r="P23" s="122" t="s">
-        <v>88</v>
+      <c r="P23" s="120" t="s">
+        <v>87</v>
       </c>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
@@ -5320,25 +5308,25 @@
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
-      <c r="I24" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="123" t="s">
+      <c r="I24" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N24" s="43"/>
       <c r="O24" s="43"/>
-      <c r="P24" s="122" t="s">
-        <v>119</v>
+      <c r="P24" s="120" t="s">
+        <v>117</v>
       </c>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18"/>
       <c r="T24" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
@@ -5348,7 +5336,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -5356,37 +5344,37 @@
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
       <c r="H25" s="32"/>
-      <c r="I25" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="123" t="s">
+      <c r="I25" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N25" s="43"/>
       <c r="O25" s="43"/>
       <c r="P25" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18"/>
       <c r="T25" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="U25" s="18"/>
       <c r="V25" s="18"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="13:15">
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A27" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -5408,7 +5396,7 @@
       <c r="S27" s="30"/>
       <c r="T27" s="30"/>
       <c r="U27" s="30"/>
-      <c r="V27" s="61"/>
+      <c r="V27" s="60"/>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="1:22">
       <c r="A28" s="17" t="s">
@@ -5440,11 +5428,11 @@
       <c r="Q28" s="42"/>
       <c r="R28" s="42"/>
       <c r="S28" s="42"/>
-      <c r="T28" s="54" t="s">
+      <c r="T28" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="U28" s="59"/>
-      <c r="V28" s="60"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="59"/>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="1:22">
       <c r="A29" s="18">
@@ -5459,25 +5447,25 @@
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
-      <c r="I29" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="123" t="s">
+      <c r="I29" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N29" s="43"/>
       <c r="O29" s="43"/>
-      <c r="P29" s="122" t="s">
-        <v>88</v>
+      <c r="P29" s="120" t="s">
+        <v>87</v>
       </c>
       <c r="Q29" s="18"/>
       <c r="R29" s="18"/>
       <c r="S29" s="18"/>
       <c r="T29" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="U29" s="18"/>
       <c r="V29" s="18"/>
@@ -5487,7 +5475,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -5495,25 +5483,25 @@
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
-      <c r="I30" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="123" t="s">
+      <c r="I30" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N30" s="43"/>
       <c r="O30" s="43"/>
-      <c r="P30" s="122" t="s">
-        <v>119</v>
+      <c r="P30" s="120" t="s">
+        <v>117</v>
       </c>
       <c r="Q30" s="18"/>
       <c r="R30" s="18"/>
       <c r="S30" s="18"/>
       <c r="T30" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U30" s="18"/>
       <c r="V30" s="18"/>
@@ -5523,7 +5511,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -5531,25 +5519,25 @@
       <c r="F31" s="25"/>
       <c r="G31" s="25"/>
       <c r="H31" s="33"/>
-      <c r="I31" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="123" t="s">
+      <c r="I31" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N31" s="43"/>
       <c r="O31" s="43"/>
       <c r="P31" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="18"/>
       <c r="R31" s="18"/>
       <c r="S31" s="18"/>
-      <c r="T31" s="122" t="s">
-        <v>127</v>
+      <c r="T31" s="120" t="s">
+        <v>125</v>
       </c>
       <c r="U31" s="18"/>
       <c r="V31" s="18"/>
@@ -5559,7 +5547,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -5567,25 +5555,25 @@
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
       <c r="H32" s="33"/>
-      <c r="I32" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="123" t="s">
+      <c r="I32" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N32" s="43"/>
       <c r="O32" s="43"/>
       <c r="P32" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="18"/>
       <c r="R32" s="18"/>
       <c r="S32" s="18"/>
       <c r="T32" s="18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U32" s="18"/>
       <c r="V32" s="18"/>
@@ -5595,7 +5583,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -5603,25 +5591,25 @@
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
       <c r="H33" s="33"/>
-      <c r="I33" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="123" t="s">
+      <c r="I33" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="121" t="s">
         <v>52</v>
       </c>
       <c r="N33" s="43"/>
       <c r="O33" s="43"/>
       <c r="P33" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="18"/>
       <c r="R33" s="18"/>
       <c r="S33" s="18"/>
       <c r="T33" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>

--- a/docs/設計/製品在庫管理/基本設計書_製品在庫照会API .xlsx
+++ b/docs/設計/製品在庫管理/基本設計書_製品在庫照会API .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7575" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19815" windowHeight="7575" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -314,7 +314,7 @@
     <t>正常系メッセージ</t>
   </si>
   <si>
-    <t>"部品在庫情報を正常に取得しました"</t>
+    <t>"製品在庫情報を正常に取得しました"</t>
   </si>
   <si>
     <t>data</t>
@@ -476,10 +476,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -537,26 +537,19 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -567,9 +560,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -583,24 +591,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -622,6 +615,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -635,20 +651,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -657,11 +659,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -673,9 +674,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -715,13 +715,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +739,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,109 +871,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,37 +883,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1048,6 +1048,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1059,21 +1098,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1093,35 +1117,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1137,11 +1139,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1150,148 +1150,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
